--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -515,12 +515,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Lagerplatz</t>
+          <t>Das Lager</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Weidenland</t>
+          <t>Trümmerebene</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -543,24 +543,24 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Eine Feuerstelle unter alten Weiden. Hier beginnt jeder Weg.</t>
+          <t>Eine Feuerstelle zwischen umgestürzten Säulen. Hier beginnt jeder Weg.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>birkenhain</t>
+          <t>quarzhang</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Birkenhain</t>
+          <t>Quarzhang</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Weidenland</t>
+          <t>Trümmerebene</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -583,7 +583,7 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Helle Stämme, trockenes Holz am Boden.</t>
+          <t>Helle Kristalle wachsen aus dem Geröll, kalt und klar.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Weidenland</t>
+          <t>Trümmerebene</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -630,17 +630,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>weidenufer</t>
+          <t>stillesufer</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Weidenufer</t>
+          <t>Stilles Ufer</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Weidenland</t>
+          <t>Trümmerebene</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -718,12 +718,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>spalt</t>
+          <t>echohoehle</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Der Spalt</t>
+          <t>Echohöhle</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -732,14 +732,14 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ort</t>
+          <t>hoehle</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -751,19 +751,19 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Zwei Felswände, kaum eine Schulter breit auseinander.</t>
+          <t>Jeder Schritt kommt dreimal zurück, jedes Mal etwas fremder.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>stillequelle</t>
+          <t>spalt</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Stille Quelle</t>
+          <t>Der Spalt</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -791,19 +791,19 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Ein Becken ohne Wellen. Man hört den eigenen Atem.</t>
+          <t>Zwei Felswände, kaum eine Schulter breit auseinander.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>dornenhecke</t>
+          <t>stillequelle</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Dornenhecke</t>
+          <t>Stille Quelle</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -812,42 +812,38 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>dornenfluesterer, hastwind, gruebelkraehe</t>
-        </is>
-      </c>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Ein Pfad, der sich jeden Tag ein wenig schließt.</t>
+          <t>Ein Becken ohne Wellen. Man hört den eigenen Atem.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>mondsee</t>
+          <t>dornengrat</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Mondsee</t>
+          <t>Dornengrat</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -856,10 +852,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -873,113 +869,109 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>echo, nebelwicht, schwerer-schatten</t>
+          <t>dornenfluesterer, hastwind, gruebelkraehe</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Nachts spiegelt er Dinge, die nicht da sind.</t>
+          <t>Ein Grat aus schwarzen Splittern, der sich jeden Tag ein wenig schließt.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>schlucht</t>
+          <t>mondsee</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Die Schlucht</t>
+          <t>Mondsee</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Grenzland</t>
+          <t>Nebelmark</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ort</t>
+          <t>wild</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>echo, nebelwicht, schwerer-schatten</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Unten rauscht etwas. Die alte Brücke hängt in Fetzen.</t>
+          <t>Nachts spiegelt er Dinge, die nicht da sind.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>aschenhang</t>
+          <t>schlucht</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Aschenhang</t>
+          <t>Die Schlucht</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Aschenland</t>
+          <t>Grenzland</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>schwerer-schatten, glutfresser, echo</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>quest:q-bruecke</t>
-        </is>
-      </c>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Grauer Staub, warm unter den Füßen.</t>
+          <t>Unten rauscht etwas. Von der alten Brücke hängen nur Ketten.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>turm</t>
+          <t>aschenhang</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Turm der Stufen</t>
+          <t>Aschenhang</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -988,22 +980,26 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ort</t>
+          <t>wild</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>schwerer-schatten, glutfresser, echo</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>quest:q-bruecke</t>
@@ -1011,31 +1007,31 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Niemand weiß, wie viele Stufen es sind. Man zählt beim Gehen.</t>
+          <t>Grauer Staub, warm unter den Füßen. Weiter oben ein Thron.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>langestrasse</t>
+          <t>turm</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Die lange Straße</t>
+          <t>Turm der Stufen</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Grenzland</t>
+          <t>Aschenland</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1055,53 +1051,97 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Gerade, gepflastert, ohne sichtbares Ende.</t>
+          <t>Niemand weiß, wie viele Stufen es sind. Man zählt beim Gehen.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>langestrasse</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Die lange Straße</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Grenzland</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ort</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>quest:q-bruecke</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Gerade, gepflastert, ohne sichtbares Ende.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>weisstal</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Weißes Tal</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Nordland</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D16" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>wild</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>nachtmahr, die-leere</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>quest:q-langestrasse</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Schnee, der nicht knirscht.</t>
         </is>
@@ -1110,7 +1150,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"lager,wild,sammeln,ort"</formula1>
+      <formula1>"lager,wild,sammeln,ort,hoehle"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
@@ -1223,7 +1263,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>glimmer:2-4, item:4</t>
+          <t>aether:2-4, item:4</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -1267,7 +1307,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>glimmer:3-6, item:5</t>
+          <t>aether:3-6, item:5</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -1311,7 +1351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>glimmer:3-5, holz:0-1, item:5</t>
+          <t>aether:3-5, quarz:0-1, item:5</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1355,7 +1395,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>glimmer:4-7, item:6</t>
+          <t>aether:4-7, item:6</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1399,7 +1439,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>glimmer:6-10, item:10</t>
+          <t>aether:6-10, item:10</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1443,7 +1483,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>glimmer:5-9, holz:0-2, item:8</t>
+          <t>aether:5-9, quarz:0-2, item:8</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1487,7 +1527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>glimmer:6-11, stein:0-2, item:8</t>
+          <t>aether:6-11, stein:0-2, item:8</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1531,7 +1571,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>glimmer:8-13, item:9</t>
+          <t>aether:8-13, item:9</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1575,7 +1615,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>glimmer:9-15, stein:1-2, item:10</t>
+          <t>aether:9-15, stein:1-2, item:10</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1619,7 +1659,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>glimmer:11-18, item:12</t>
+          <t>aether:11-18, item:12</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1663,7 +1703,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>glimmer:20-30, item:25</t>
+          <t>aether:20-30, item:25</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1707,7 +1747,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>glimmer:30-45, item:30</t>
+          <t>aether:30-45, item:30</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1737,22 +1777,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1773,50 +1816,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>art</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>monster</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>pruefungen</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>bedingung</t>
+          <t>voraussetzung</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>dauer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ertrag</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>verbrauch</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>kosten</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>belohnung</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>wiederholbar</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>abklingzeit</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>notiz</t>
         </is>
@@ -1825,45 +1883,62 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>q-holz</t>
+          <t>q-quarz</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Holz sammeln</t>
+          <t>Quarz brechen</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>birkenhain</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Trockene Äste aufsammeln und zum Bündel schnüren. Mehr Kraft, mehr Holz.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>quarzhang</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>sammeln</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Klare Kristalle aus dem Geröll lösen.</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="n">
-        <v>3</v>
+      <c r="H2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>holz:2-4</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>quarz:2-4</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1881,32 +1956,49 @@
           <t>steinbruch</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Lose Blöcke lösen und handlich schlagen. Mehr Kraft, mehr Stein.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sammeln</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Lose Blöcke lösen und handlich schlagen.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="n">
-        <v>3</v>
+      <c r="H3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>stein:1-3</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>stein:2-4</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1924,83 +2016,113 @@
           <t>lager</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Unter den Weiden ist Platz für ein Zelt. Es fehlt nur das Material.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>bauen</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Zwischen den Säulen ist Platz für ein Zelt. Es fehlt nur das Material.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>holz:6, stein:3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>quarz:6, stein:6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>freischaltung:zuhause, glimmer:10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>freischaltung:zuhause, aether:10</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>q-baum</t>
+          <t>q-saeule</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Der umgestürzte Baum</t>
+          <t>Die umgestürzte Säule</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>weidenufer</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Ein Stamm liegt quer über dem Pfad. Wer ihn bewegt, hat Brennholz für Tage.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>kraft:3</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="n">
+          <t>stillesufer</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Eine Säule liegt quer über dem Pfad. Wer sie zerlegt, hat Stein für Tage.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=3</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>stein:4-6, aether:4</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>holz:5-7, glimmer:4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2018,495 +2140,680 @@
           <t>nebelfurt</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>kampf</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>In der Furt ruft jemand um Hilfe. Ein Wagen steckt fest, und davor steht etwas Großes.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>nebelwaechter</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit:3</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="n">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=3, ausdauer&gt;=3</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>freischaltung:haendler, glimmer:25</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>freischaltung:haendler, aether:25</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>q-spalt</t>
+          <t>q-echohoehle</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Durch den Spalt</t>
+          <t>Die Echohöhle</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>spalt</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>echohoehle</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>hoehle</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an seinen Werten.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit:4</t>
+          <t>zauderling, nebelwicht, gruebelkraehe, hastwind, dornenfluesterer</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit&gt;=3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="n">
+          <t>kraft&gt;=2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>aether:30, item:beine_kampfhose_2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>glimmer:15, item:kopf_stirnband_1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>q-quelle</t>
+          <t>q-spalt</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Die stille Quelle</t>
+          <t>Durch den Spalt</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>stillequelle</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit:3, gelassenheit:5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="n">
+          <t>spalt</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit&gt;=4</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>glimmer:8, rast:1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>aether:15, item:kopf_stirnband_1</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>q-dornen</t>
+          <t>q-quelle</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Der Weg durch die Dornen</t>
+          <t>Die stille Quelle</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>dornenhecke</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Die Hecke flüstert. Ein Weg führt hindurch, wenn man sich weder hetzen noch festhalten lässt.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>beweglichkeit:5, gelassenheit:4</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="n">
+          <t>stillequelle</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit&gt;=3</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>aether:8, rast:1</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>glimmer:20, einrichtung:windspiel</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>q-bruecke</t>
+          <t>q-dornen</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Die Brücke über die Schlucht</t>
+          <t>Über den Dornengrat</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>schlucht</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Mit Holz, Stein und einem langen Atem lässt sich die Brücke flicken.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>ausdauer:5, kraft:4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>holz:10, stein:4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>4</v>
+          <t>dornengrat</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Der Grat flüstert. Hinüber kommt, wer sich weder hetzen noch festhalten lässt.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit&gt;=5, gelassenheit&gt;=4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>glimmer:30</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>aether:20, einrichtung:windspiel</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>q-mondsee</t>
+          <t>q-bruecke</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Spiegel im Mondsee</t>
+          <t>Die Brücke über die Schlucht</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>mondsee</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>echo</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit:6</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>glimmer:35, item:kopf_stillemaske_3</t>
-        </is>
-      </c>
+          <t>schlucht</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>bauen</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Mit Stein, Quarz und einem langen Atem lässt sich die Brücke neu legen.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer&gt;=5, kraft&gt;=4</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t>quarz:10, stein:12</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>aether:30</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>q-turm</t>
+          <t>q-mondsee</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Der Turm der Stufen</t>
+          <t>Spiegel im Mondsee</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>turm</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>mondsee</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>kampf</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ausdauer:7</t>
+          <t>echo</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>summe_stockwerke&gt;=100</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>glimmer:60, item:schuhe_leichtestiefel_3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+          <t>gelassenheit&gt;=6</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>aether:35, item:kopf_stillemaske_3</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="O12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>q-langestrasse</t>
+          <t>q-turm</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Die lange Straße</t>
+          <t>Der Turm der Stufen</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>langestrasse</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Die Straße endet nur für die, die schon viele Kilometer in den Beinen haben.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>ausdauer:6</t>
-        </is>
-      </c>
+          <t>turm</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>summe_km&gt;=30</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="n">
+          <t>summe_stockwerke&gt;=100</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>glimmer:40</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>aether:60, item:schuhe_leichtestiefel_3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>q-koenigin</t>
+          <t>q-langestrasse</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Die Königin in der Asche</t>
+          <t>Die lange Straße</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>aschenhang</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Im Zentrum des Hangs sitzt sie auf einem Thron aus kalter Glut.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>glutfresser, aschenkoenigin</t>
+          <t>langestrasse</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Die Straße endet nur für die, die schon viele Kilometer in den Beinen haben.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=8</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="n">
-        <v>5</v>
+          <t>summe_km&gt;=30</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>glimmer:120, item:handschuhe_glimmerwickel_4, einrichtung:glimmerschale</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>aether:40</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>q-aschenthron</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Der Aschenthron</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>aschenhang</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>hoehle</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Der Weg zum Thron führt an drei Wächtern vorbei. Oben sitzt sie, auf kalter Glut.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>schwerer-schatten, glutfresser, glutfresser, aschenkoenigin</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=8</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>aether:120, item:handschuhe_aetherwickel_4, einrichtung:aetherschale</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>q-leere</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Das weiße Schweigen</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>weisstal</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>kampf</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Im Tal wartet etwas, das man nicht besiegen muss.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>die-leere</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>gelassenheit&gt;=10</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
+      <c r="H16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>glimmer:200</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>aether:200</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"sammeln,erkunden,kampf,hoehle,bauen"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2527,7 +2834,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
@@ -2548,7 +2855,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>holz</t>
+          <t>quarz</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2558,7 +2865,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>glimmer</t>
+          <t>aether</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2616,7 +2923,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Zwei Stangen, eine Plane, ein trockener Boden.</t>
+          <t>Eine Plane zwischen zwei Säulen, ein trockener Boden.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -2631,14 +2938,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Hütte</t>
+          <t>Steinhütte</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>40</v>
@@ -2654,7 +2961,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Vier Wände aus Holz und eine Tür, die schließt.</t>
+          <t>Vier Wände aus gestapeltem Stein und eine Tür, die schließt.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -2673,10 +2980,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>100</v>
@@ -2714,7 +3021,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>250</v>
@@ -2730,7 +3037,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Mauern, die den Wind nicht hereinlassen.</t>
+          <t>Feste Mauern, Fenster aus Quarz, die das Licht weich machen.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2948,7 +3255,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Riecht nach Sommer.</t>
+          <t>Riecht nach einem Sommer, den es hier nie gab.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -3155,7 +3462,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Regal</t>
+          <t>Steinregal</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3226,12 +3533,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>glimmerschale</t>
+          <t>aetherschale</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Glimmerschale</t>
+          <t>Ätherschale</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3257,7 +3564,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_glimmerschale.png</t>
+          <t>icon_einrichtung_aetherschale.png</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3307,7 +3614,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung bestimmt, wie viel Ausdauer die Reise kostet.</t>
+          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung zum Lager bestimmt Reisezeit und Ausdauer.</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3626,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>lager (Startpunkt, dort steht das Zuhause), wild (Geister tauchen auf), sammeln (Holz oder Stein), ort (feste Quests).</t>
+          <t>lager (Ausgangspunkt jeder Expedition, dort steht das Zuhause), wild (Geister tauchen auf), sammeln (Quarz oder Stein), hoehle (mehrere Geister nacheinander), ort (feste Quests).</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3638,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ja = hier können täglich zufällige Begegnungen erscheinen.</t>
+          <t>ja = hier können täglich Geister erscheinen.</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3682,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Stärke. Zufällige Begegnungen liegen nahe am Durchschnitt der vier Stats.</t>
+          <t>Stärke. Begegnungen liegen nahe am Durchschnitt der vier Werte.</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3694,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lebenspunkte, Schaden je Treffer, Geschick (gegen Beweglichkeit gewürfelt).</t>
+          <t>Lebenspunkte, Schaden je Treffer, Geschick (gegen Beweglichkeit gewürfelt). Bestimmen, wie lange ein Kampf dauert.</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3706,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ja = mit Gelassenheit kann der Geist beruhigt statt besiegt werden.</t>
+          <t>ja = mit Gelassenheit kann der Geist beruhigt statt besiegt werden (mehr Äther).</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3718,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>glimmer:2-4, holz:0-1, stein:0-1, item:5 (Prozent-Chance auf ein Ausrüstungsteil).</t>
+          <t>aether:2-4, quarz:0-1, stein:0-1, item:5 (Prozent-Chance auf ein Ausrüstungsteil).</t>
         </is>
       </c>
     </row>
@@ -3426,158 +3733,182 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pruefungen</t>
+          <t>art</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Würfelproben, alle müssen gelingen: kraft:4, gelassenheit:3 … Die Zahl ist die Schwierigkeit.</t>
+          <t>sammeln, erkunden, kampf (ein Geist), hoehle (mehrere Geister nacheinander, so weit die Werte reichen), bauen (verbraucht Material).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>monster</t>
+          <t>voraussetzung</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Kämpfe nach den Proben, der Reihe nach.</t>
+          <t>Was nötig ist, um aufzubrechen: kraft&gt;=3, quest:q-spalt, summe_km&gt;=30, summe_stockwerke&gt;=100. Scheitern gibt es nicht.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bedingung</t>
+          <t>dauer</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Voraussetzung, um die Quest überhaupt zu beginnen: beweglichkeit&gt;=3, quest:q-spalt, summe_km&gt;=30, summe_stockwerke&gt;=100.</t>
+          <t>Minuten vor Ort bei Werten auf 1. Bei Kampf und Höhle kommt die Kampfzeit dazu.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>verbrauch</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Material, das die Quest verbraucht: holz:6, stein:3.</t>
+          <t>Werte, die die Zeit vor Ort verkürzen (4 % je Level, höchstens auf die Hälfte).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kosten</t>
+          <t>ertrag</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Ausdauer aus der Leiste für einen Versuch.</t>
+          <t>Werte, die mehr Ertrag bringen (beim Sammeln +1 je 3 Level, sonst +5 % Äther je Level).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>belohnung</t>
+          <t>verbrauch</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>glimmer:20, holz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll).</t>
+          <t>Material, das die Quest verbraucht: quarz:6, stein:6.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wiederholbar, abklingzeit</t>
+          <t>kosten</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ja = kann erneut gemacht werden, frühestens nach so vielen Tagen.</t>
+          <t>Ausdauer für die Arbeit vor Ort. Hin- und Rückweg kommen nach Entfernung dazu.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZUHAUSE</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr"/>
+          <t>belohnung</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>aether:20, quarz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>holz, stein, glimmer</t>
+          <t>wiederholbar, abklingzeit</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Kosten für den Ausbau auf diese Stufe. Stufe 1 entsteht durch die Quest.</t>
+          <t>ja = kann erneut gemacht werden, frühestens nach so vielen Tagen.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>erholung</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Prozent schneller füllt sich die Ausdauerleiste.</t>
-        </is>
-      </c>
+          <t>ZUHAUSE</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>plaetze, schrank</t>
+          <t>quarz, stein, aether</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Plätze für Einrichtung, Fächer im Schrank.</t>
+          <t>Kosten für den Ausbau auf diese Stufe. Stufe 1 entsteht durch die Quest.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EINRICHTUNG</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr"/>
+          <t>erholung</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Prozent schneller füllt sich die Ausdauerleiste.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>effekt</t>
+          <t>plaetze, schrank</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>erholung:+5 und/oder glueck:+3 (Prozent).</t>
+          <t>Plätze für Einrichtung, Fächer im Schrank.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>EINRICHTUNG</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>effekt</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>erholung:+5 und/oder glueck:+3 (Prozent).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>ab_stufe</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Ab welcher Stufe des Zuhauses sie aufgestellt werden kann.</t>
         </is>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -550,12 +550,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>quarzhang</t>
+          <t>pilzhain</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Quarzhang</t>
+          <t>Pilzhain</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -583,7 +583,7 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Helle Kristalle wachsen aus dem Geröll, kalt und klar.</t>
+          <t>Zwischen den Trümmern stehen Pilze, hoch wie Säulen. Ihre Stiele sind leicht und zäh.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>aether:3-5, quarz:0-1, item:5</t>
+          <t>aether:3-5, pilzholz:0-1, item:5</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>aether:5-9, quarz:0-2, item:8</t>
+          <t>aether:5-9, pilzholz:0-2, item:8</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1883,17 +1883,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>q-quarz</t>
+          <t>q-pilzholz</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Quarz brechen</t>
+          <t>Pilzholz schlagen</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>quarzhang</t>
+          <t>pilzhain</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Klare Kristalle aus dem Geröll lösen.</t>
+          <t>Einen Stiel fällen und in leichte, handliche Stücke teilen.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>quarz:2-4</t>
+          <t>pilzholz:2-4</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>quarz:6, stein:6</t>
+          <t>pilzholz:6, stein:6</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mit Stein, Quarz und einem langen Atem lässt sich die Brücke neu legen.</t>
+          <t>Mit Pilzholz, Stein und einem langen Atem lässt sich die Brücke neu legen.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>quarz:10, stein:12</t>
+          <t>pilzholz:10, stein:12</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>quarz</t>
+          <t>pilzholz</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Feste Mauern, Fenster aus Quarz, die das Licht weich machen.</t>
+          <t>Feste Mauern, Balken aus Pilzholz, ein Dach, das hält.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>lager (Ausgangspunkt jeder Expedition, dort steht das Zuhause), wild (Geister tauchen auf), sammeln (Quarz oder Stein), hoehle (mehrere Geister nacheinander), ort (feste Quests).</t>
+          <t>lager (Ausgangspunkt jeder Expedition, dort steht das Zuhause), wild (Geister tauchen auf), sammeln (Pilzholz oder Stein), hoehle (mehrere Geister nacheinander), ort (feste Quests).</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>aether:2-4, quarz:0-1, stein:0-1, item:5 (Prozent-Chance auf ein Ausrüstungsteil).</t>
+          <t>aether:2-4, pilzholz:0-1, stein:0-1, item:5 (Prozent-Chance auf ein Ausrüstungsteil).</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Material, das die Quest verbraucht: quarz:6, stein:6.</t>
+          <t>Material, das die Quest verbraucht: pilzholz:6, stein:6.</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>aether:20, quarz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
+          <t>aether:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>quarz, stein, aether</t>
+          <t>pilzholz, stein, aether</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -1263,7 +1263,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>aether:2-4, item:4</t>
+          <t>splitter:2-4, item:4</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>aether:3-6, item:5</t>
+          <t>splitter:3-6, item:5</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>aether:3-5, pilzholz:0-1, item:5</t>
+          <t>splitter:3-5, pilzholz:0-1, item:5</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>aether:4-7, item:6</t>
+          <t>splitter:4-7, item:6</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>aether:6-10, item:10</t>
+          <t>splitter:6-10, item:10</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>aether:5-9, pilzholz:0-2, item:8</t>
+          <t>splitter:5-9, pilzholz:0-2, item:8</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>aether:6-11, stein:0-2, item:8</t>
+          <t>splitter:6-11, stein:0-2, item:8</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>aether:8-13, item:9</t>
+          <t>splitter:8-13, item:9</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>aether:9-15, stein:1-2, item:10</t>
+          <t>splitter:9-15, stein:1-2, item:10</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>aether:11-18, item:12</t>
+          <t>splitter:11-18, item:12</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>aether:20-30, item:25</t>
+          <t>splitter:20-30, item:25</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>aether:30-45, item:30</t>
+          <t>splitter:30-45, item:30</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>freischaltung:zuhause, aether:10</t>
+          <t>freischaltung:zuhause, splitter:10</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>stein:4-6, aether:4</t>
+          <t>stein:4-6, splitter:4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>freischaltung:haendler, aether:25</t>
+          <t>freischaltung:haendler, splitter:25</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>aether:30, item:beine_kampfhose_2</t>
+          <t>splitter:30, item:beine_kampfhose_2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>aether:15, item:kopf_stirnband_1</t>
+          <t>splitter:15, item:kopf_stirnband_1</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>aether:8, rast:1</t>
+          <t>splitter:8, rast:1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>aether:20, einrichtung:windspiel</t>
+          <t>splitter:20, einrichtung:windspiel</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>aether:30</t>
+          <t>splitter:30</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>aether:35, item:kopf_stillemaske_3</t>
+          <t>splitter:35, item:kopf_stillemaske_3</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>aether:60, item:schuhe_leichtestiefel_3</t>
+          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>aether:40</t>
+          <t>splitter:40</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>aether:120, item:handschuhe_aetherwickel_4, einrichtung:aetherschale</t>
+          <t>splitter:120, item:handschuhe_nebelwickel_4, einrichtung:splitterschale</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>aether:200</t>
+          <t>splitter:200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>aether</t>
+          <t>splitter</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -3533,12 +3533,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>aetherschale</t>
+          <t>splitterschale</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Ätherschale</t>
+          <t>Splitterschale</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Eine Schale voller Licht, das nicht ausgeht.</t>
+          <t>Eine Schale voller Traumsplitter, die nie ganz erlöschen.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_aetherschale.png</t>
+          <t>icon_einrichtung_splitterschale.png</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ja = mit Gelassenheit kann der Geist beruhigt statt besiegt werden (mehr Äther).</t>
+          <t>ja = mit Gelassenheit kann der Geist beruhigt statt besiegt werden (mehr Traumsplitter).</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>aether:2-4, pilzholz:0-1, stein:0-1, item:5 (Prozent-Chance auf ein Ausrüstungsteil).</t>
+          <t>splitter:2-4, pilzholz:0-1, stein:0-1, item:5 (Prozent-Chance auf ein Ausrüstungsteil).</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Werte, die mehr Ertrag bringen (beim Sammeln +1 je 3 Level, sonst +5 % Äther je Level).</t>
+          <t>Werte, die mehr Ertrag bringen (beim Sammeln +1 je 3 Level, sonst +5 % Traumsplitter je Level).</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>aether:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
+          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pilzholz, stein, aether</t>
+          <t>pilzholz, stein, splitter</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -3559,7 +3559,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Eine Schale voller Traumsplitter, die nie ganz erlöschen.</t>
+          <t>Eine Schale voller Bannsplitter, die nie ganz erlöschen.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ja = mit Gelassenheit kann der Geist beruhigt statt besiegt werden (mehr Traumsplitter).</t>
+          <t>ja = mit Gelassenheit kann der Geist beruhigt statt besiegt werden (mehr Bannsplitter).</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Werte, die mehr Ertrag bringen (beim Sammeln +1 je 3 Level, sonst +5 % Traumsplitter je Level).</t>
+          <t>Werte, die mehr Ertrag bringen (beim Sammeln +1 je 3 Level, sonst +5 % Bannsplitter je Level).</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -1777,25 +1777,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1836,45 +1835,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dauer</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>ertrag</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ertrag</t>
+          <t>verbrauch</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>verbrauch</t>
+          <t>kosten</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>kosten</t>
+          <t>belohnung</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>belohnung</t>
+          <t>wiederholbar</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>wiederholbar</t>
+          <t>abklingzeit</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>abklingzeit</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>notiz</t>
         </is>
@@ -1883,12 +1877,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>q-pilzholz</t>
+          <t>q-pilzholz-klein</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pilzholz schlagen</t>
+          <t>Pilzholz auflesen</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1903,57 +1897,50 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Einen Stiel fällen und in leichte, handliche Stücke teilen.</t>
+          <t>Was der Wind von den Hüten gebrochen hat, liegt leicht im Moos.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>kraft, ausdauer</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
           <t>kraft</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="n">
-        <v>2</v>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>pilzholz:1</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:2-4</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>q-stein</t>
+          <t>q-pilzholz</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Steine brechen</t>
+          <t>Pilzholz schlagen</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>steinbruch</t>
+          <t>pilzhain</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1963,73 +1950,76 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Lose Blöcke lösen und handlich schlagen.</t>
+          <t>Einen Stiel fällen und in leichte, handliche Stücke teilen.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="n">
-        <v>15</v>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>kraft</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>kraft</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
-        <v>2</v>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>pilzholz:2-3</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>stein:2-4</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>q-zuhause</t>
+          <t>q-pilzholz-gross</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ein Platz zum Bleiben</t>
+          <t>Einen Riesenpilz fällen</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>lager</t>
+          <t>pilzhain</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>bauen</t>
+          <t>sammeln</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Zwischen den Säulen ist Platz für ein Zelt. Es fehlt nur das Material.</t>
+          <t>Ein ganzer Stamm, so hoch wie eine Säule. Das Holz reicht für eine Wand.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -2037,291 +2027,266 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>pilzholz:6, stein:6</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>2</v>
+      <c r="K4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>pilzholz:7-9</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>freischaltung:zuhause, splitter:10</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>q-saeule</t>
+          <t>q-stein-klein</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Die umgestürzte Säule</t>
+          <t>Lose Steine auflesen</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>stillesufer</t>
+          <t>steinbruch</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>sammeln</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Eine Säule liegt quer über dem Pfad. Wer sie zerlegt, hat Stein für Tage.</t>
+          <t>Am Rand des Bruchs liegt, was von allein herabgefallen ist.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>kraft&gt;=3</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>kraft</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>kraft</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="n">
-        <v>2</v>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>stein:1</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>stein:4-6, splitter:4</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>q-haendler</t>
+          <t>q-stein</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Der Händler im Nebel</t>
+          <t>Steine brechen</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>nebelfurt</t>
+          <t>steinbruch</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>sammeln</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>In der Furt ruft jemand um Hilfe. Ein Wagen steckt fest, und davor steht etwas Großes.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>nebelwaechter</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>kraft&gt;=3, ausdauer&gt;=3</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>Lose Blöcke lösen und handlich schlagen.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="n">
-        <v>3</v>
+      <c r="K6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>stein:2-3</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>freischaltung:haendler, splitter:25</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n">
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>q-echohoehle</t>
+          <t>q-stein-gross</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Die Echohöhle</t>
+          <t>Einen Block lösen</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>echohoehle</t>
+          <t>steinbruch</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>hoehle</t>
+          <t>sammeln</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an seinen Werten.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>zauderling, nebelwicht, gruebelkraehe, hastwind, dornenfluesterer</t>
-        </is>
-      </c>
+          <t>Ein Block aus der Wand, sauber gespalten. Schwer, aber er trägt ein Haus.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>kraft&gt;=5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="n">
-        <v>3</v>
+      <c r="K7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>stein:7-9</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>splitter:30, item:beine_kampfhose_2</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>q-spalt</t>
+          <t>q-zuhause</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Durch den Spalt</t>
+          <t>Ein Platz zum Bleiben</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>spalt</t>
+          <t>lager</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>bauen</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
+          <t>Zwischen den Säulen ist Platz für ein Zelt. Es fehlt nur das Material.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>beweglichkeit&gt;=4</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>beweglichkeit</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>2</v>
+          <t>pilzholz:6, stein:6</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>freischaltung:zuhause, splitter:10</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>splitter:15, item:kopf_stirnband_1</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>q-quelle</t>
+          <t>q-uferkies</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Die stille Quelle</t>
+          <t>Splitter im Uferkies</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>stillequelle</t>
+          <t>stillesufer</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2331,61 +2296,50 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
+          <t>Wo früher Geister gebannt wurden, glimmen noch Splitter zwischen den Kieseln.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit&gt;=3</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>25</v>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>gelassenheit</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="n">
-        <v>1</v>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>splitter:1</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>splitter:8, rast:1</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>q-dornen</t>
+          <t>q-saeule</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Über den Dornengrat</t>
+          <t>Die umgestürzte Säule</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>dornengrat</t>
+          <t>stillesufer</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2395,249 +2349,233 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Der Grat flüstert. Hinüber kommt, wer sich weder hetzen noch festhalten lässt.</t>
+          <t>Eine Säule liegt quer über dem Pfad. Wer sie zerlegt, hat Stein für Tage.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit&gt;=5, gelassenheit&gt;=4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
+          <t>kraft&gt;=3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="n">
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>stein:4-6, splitter:4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>splitter:20, einrichtung:windspiel</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>q-bruecke</t>
+          <t>q-haendler</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Die Brücke über die Schlucht</t>
+          <t>Der Händler im Nebel</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>schlucht</t>
+          <t>nebelfurt</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>bauen</t>
+          <t>kampf</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mit Pilzholz, Stein und einem langen Atem lässt sich die Brücke neu legen.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
+          <t>In der Furt ruft jemand um Hilfe. Ein Wagen steckt fest, und davor steht etwas Großes.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>nebelwaechter</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ausdauer&gt;=5, kraft&gt;=4</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>kraft, ausdauer</t>
-        </is>
-      </c>
+          <t>kraft&gt;=3, ausdauer&gt;=3</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>pilzholz:10, stein:12</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>4</v>
+      <c r="K11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>freischaltung:haendler, splitter:25</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>splitter:30</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>q-mondsee</t>
+          <t>q-furtwache</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Spiegel im Mondsee</t>
+          <t>Wache an der Furt</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>mondsee</t>
+          <t>nebelfurt</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>echo</t>
-        </is>
-      </c>
+          <t>Lange am Wasser sitzen, bis der Nebel zeigt, was er mit sich trägt.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=6</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>gelassenheit&gt;=5</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>3</v>
+      <c r="K12" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>splitter:9-12</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>splitter:35, item:kopf_stillemaske_3</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>q-turm</t>
+          <t>q-echohoehle</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Der Turm der Stufen</t>
+          <t>Die Echohöhle</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>turm</t>
+          <t>echohoehle</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>hoehle</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an seinen Werten.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>zauderling, nebelwicht, gruebelkraehe, hastwind, dornenfluesterer</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>summe_stockwerke&gt;=100</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>ausdauer</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>ausdauer</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="n">
-        <v>4</v>
+          <t>kraft&gt;=2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>splitter:30, item:beine_kampfhose_2</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>q-langestrasse</t>
+          <t>q-spalt</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Die lange Straße</t>
+          <t>Durch den Spalt</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>langestrasse</t>
+          <t>spalt</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2647,173 +2585,648 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Die Straße endet nur für die, die schon viele Kilometer in den Beinen haben.</t>
+          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>summe_km&gt;=30</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>40</v>
+          <t>beweglichkeit&gt;=4</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit</t>
+        </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>ausdauer</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>ausdauer</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="n">
-        <v>4</v>
+          <t>beweglichkeit</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>splitter:15, item:kopf_stirnband_1</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>splitter:40</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>q-aschenthron</t>
+          <t>q-quelle</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Der Aschenthron</t>
+          <t>Die stille Quelle</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>aschenhang</t>
+          <t>stillequelle</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>hoehle</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Der Weg zum Thron führt an drei Wächtern vorbei. Oben sitzt sie, auf kalter Glut.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>schwerer-schatten, glutfresser, glutfresser, aschenkoenigin</t>
-        </is>
-      </c>
+          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=8</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t>gelassenheit&gt;=3</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="n">
-        <v>5</v>
+      <c r="K15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>splitter:8, rast:1</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>splitter:120, item:handschuhe_nebelwickel_4, einrichtung:splitterschale</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>q-dornen</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Über den Dornengrat</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>dornengrat</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Der Grat flüstert. Hinüber kommt, wer sich weder hetzen noch festhalten lässt.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit&gt;=5, gelassenheit&gt;=4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>splitter:20, einrichtung:windspiel</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>q-bruecke</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Die Brücke über die Schlucht</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>schlucht</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>bauen</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Mit Pilzholz, Stein und einem langen Atem lässt sich die Brücke neu legen.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer&gt;=5, kraft&gt;=4</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>pilzholz:10, stein:12</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>splitter:30</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>q-mondsee</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Spiegel im Mondsee</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>mondsee</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>kampf</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>echo</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit&gt;=6</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>splitter:35, item:kopf_stillemaske_3</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>q-mondnacht</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Eine Nacht am Mondsee</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>mondsee</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Bis der Mond über das Wasser gewandert ist. Was dann im Uferschlamm liegt, hat lange gewartet.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>quest:q-mondsee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>splitter:15-19</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>q-turm</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Der Turm der Stufen</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>turm</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>summe_stockwerke&gt;=100</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>q-langestrasse</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Die lange Straße</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>langestrasse</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Die Straße endet nur für die, die schon viele Kilometer in den Beinen haben.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>summe_km&gt;=30</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>splitter:40</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>q-horizont</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Bis zum Horizont</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>langestrasse</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>erkunden</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Hinter dem Ende der Straße geht es weiter. Wer bis zum Abend läuft, kommt mit vollen Taschen zurück.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>quest:q-langestrasse</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>splitter:24-30</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>q-aschenthron</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Der Aschenthron</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>aschenhang</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>hoehle</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Der Weg zum Thron führt an drei Wächtern vorbei. Oben sitzt sie, auf kalter Glut.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>schwerer-schatten, glutfresser, glutfresser, aschenkoenigin</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=8</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>splitter:120, item:handschuhe_nebelwickel_4, einrichtung:splitterschale</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>q-leere</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Das weiße Schweigen</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>weisstal</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>kampf</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Im Tal wartet etwas, das man nicht besiegen muss.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>die-leere</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>gelassenheit&gt;=10</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>splitter:200</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="N24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"sammeln,erkunden,kampf,hoehle,bauen"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2942,13 +3355,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>10</v>
@@ -2980,13 +3393,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>15</v>
@@ -3018,13 +3431,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>22</v>
@@ -3056,13 +3469,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
@@ -3579,7 +3992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3614,7 +4027,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung zum Lager bestimmt Reisezeit und Ausdauer.</t>
+          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung zum Lager bestimmt die Ausdauer für den Weg: 20 Einheiten Entfernung = 1 Ausdauer = 1 Minute.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +4107,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lebenspunkte, Schaden je Treffer, Geschick (gegen Beweglichkeit gewürfelt). Bestimmen, wie lange ein Kampf dauert.</t>
+          <t>Lebenspunkte, Schaden je Treffer, Geschick (gegen Beweglichkeit gewürfelt). Bestimmen, wie ein Kampf ausgeht.</t>
         </is>
       </c>
     </row>
@@ -3757,12 +4170,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dauer</t>
+          <t>kosten</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Minuten vor Ort bei Werten auf 1. Bei Kampf und Höhle kommt die Kampfzeit dazu.</t>
+          <t>Ausdauer für die Arbeit vor Ort bei Werten auf 1. Jeder Punkt Ausdauer ist eine Minute: kosten 7 heißt 7 Minuten vor Ort. Hin- und Rückweg kommen nach Entfernung dazu.</t>
         </is>
       </c>
     </row>
@@ -3774,7 +4187,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Werte, die die Zeit vor Ort verkürzen (4 % je Level, höchstens auf die Hälfte).</t>
+          <t>Werte, die die Arbeit vor Ort kürzer und damit billiger machen (4 % je Level, höchstens auf die Hälfte).</t>
         </is>
       </c>
     </row>
@@ -3786,7 +4199,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Werte, die mehr Ertrag bringen (beim Sammeln +1 je 3 Level, sonst +5 % Bannsplitter je Level).</t>
+          <t>Werte, die mehr Ertrag bringen: +5 % je Level, beim Sammeln auf die Stücke, beim Erkunden auf die Bannsplitter.</t>
         </is>
       </c>
     </row>
@@ -3805,110 +4218,98 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kosten</t>
+          <t>belohnung</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Ausdauer für die Arbeit vor Ort. Hin- und Rückweg kommen nach Entfernung dazu.</t>
+          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>belohnung</t>
+          <t>wiederholbar, abklingzeit</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
+          <t>ja = kann erneut gemacht werden, frühestens nach so vielen Tagen.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>wiederholbar, abklingzeit</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ja = kann erneut gemacht werden, frühestens nach so vielen Tagen.</t>
-        </is>
-      </c>
+          <t>ZUHAUSE</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZUHAUSE</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
+          <t>pilzholz, stein, splitter</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Kosten für den Ausbau auf diese Stufe. Stufe 1 entsteht durch die Quest.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pilzholz, stein, splitter</t>
+          <t>erholung</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Kosten für den Ausbau auf diese Stufe. Stufe 1 entsteht durch die Quest.</t>
+          <t>Prozent schneller füllt sich die Ausdauerleiste.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>erholung</t>
+          <t>plaetze, schrank</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Prozent schneller füllt sich die Ausdauerleiste.</t>
+          <t>Plätze für Einrichtung, Fächer im Schrank.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>plaetze, schrank</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Plätze für Einrichtung, Fächer im Schrank.</t>
-        </is>
-      </c>
+          <t>EINRICHTUNG</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EINRICHTUNG</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr"/>
+          <t>effekt</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>erholung:+5 und/oder glueck:+3 (Prozent).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>effekt</t>
+          <t>ab_stufe</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>erholung:+5 und/oder glueck:+3 (Prozent).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ab_stufe</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Ab welcher Stufe des Zuhauses sie aufgestellt werden kann.</t>
         </is>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -2528,7 +2528,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an seinen Werten.</t>
+          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an den Werten.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>splitter:30</t>
+          <t>splitter:30, item:handschuhe_griffhandschuhe_2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -2239,7 +2239,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Zwischen den Säulen ist Platz für ein Zelt. Es fehlt nur das Material.</t>
+          <t>Am Feuer ist Platz für mehr. Mit Pilzholz und Stein lässt sich das Lager ausbauen.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>splitter:20, einrichtung:windspiel</t>
+          <t>splitter:20</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>splitter:120, item:handschuhe_nebelwickel_4, einrichtung:splitterschale</t>
+          <t>splitter:120, item:handschuhe_nebelwickel_4</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
+          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause (Ausbau des Lagers) oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -1777,7 +1777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1794,7 +1794,8 @@
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1870,6 +1871,11 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>notiz</t>
         </is>
       </c>
@@ -1925,7 +1931,12 @@
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1982,7 +1993,12 @@
       <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2043,7 +2059,12 @@
       <c r="N4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2096,7 +2117,12 @@
       <c r="N5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2153,7 +2179,12 @@
       <c r="N6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2214,7 +2245,12 @@
       <c r="N7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2271,7 +2307,12 @@
       <c r="N8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2324,7 +2365,12 @@
       <c r="N9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2385,7 +2431,12 @@
       <c r="N10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2442,7 +2493,12 @@
       <c r="N11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2503,7 +2559,12 @@
       <c r="N12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2560,7 +2621,12 @@
       <c r="N13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2621,7 +2687,12 @@
       <c r="N14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2682,7 +2753,12 @@
       <c r="N15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2743,7 +2819,12 @@
       <c r="N16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2804,7 +2885,12 @@
       <c r="N17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2861,7 +2947,12 @@
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2922,7 +3013,12 @@
       <c r="N19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2983,7 +3079,12 @@
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3044,7 +3145,12 @@
       <c r="N21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3105,7 +3211,12 @@
       <c r="N22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3162,7 +3273,12 @@
       <c r="N23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3219,14 +3335,22 @@
       <c r="N24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"sammeln,erkunden,kampf,hoehle,bauen"</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ja,nein"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3992,7 +4116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4242,74 +4366,86 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZUHAUSE</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>nein = die Quest bleibt in der Tabelle, wird im Spiel aber vorerst nicht angeboten. Leer = ja.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pilzholz, stein, splitter</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Kosten für den Ausbau auf diese Stufe. Stufe 1 entsteht durch die Quest.</t>
-        </is>
-      </c>
+          <t>ZUHAUSE</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>erholung</t>
+          <t>pilzholz, stein, splitter</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Prozent schneller füllt sich die Ausdauerleiste.</t>
+          <t>Kosten für den Ausbau auf diese Stufe. Stufe 1 entsteht durch die Quest.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>plaetze, schrank</t>
+          <t>erholung</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Plätze für Einrichtung, Fächer im Schrank.</t>
+          <t>Prozent schneller füllt sich die Ausdauerleiste.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EINRICHTUNG</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr"/>
+          <t>plaetze, schrank</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Plätze für Einrichtung, Fächer im Schrank.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>effekt</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>erholung:+5 und/oder glueck:+3 (Prozent).</t>
-        </is>
-      </c>
+          <t>EINRICHTUNG</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>effekt</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>erholung:+5 und/oder glueck:+3 (Prozent).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>ab_stufe</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Ab welcher Stufe des Zuhauses sie aufgestellt werden kann.</t>
         </is>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -10,9 +10,10 @@
     <sheet name="Orte" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Monster" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quests" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Zuhause" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Einrichtung" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Erklärung" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Lagerstufen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Einrichtungen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Deko" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Erklärung" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +544,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Eine Feuerstelle zwischen umgestürzten Säulen. Hier beginnt jeder Weg.</t>
+          <t>Ein offener Platz auf dem Trümmerfeld, zwischen umgestürzten Säulen und hohen Pilzen. Hier beginnt und endet jeder Weg.</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2256,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>q-zuhause</t>
+          <t>q-lagerfeuer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ein Platz zum Bleiben</t>
+          <t>Ein Lagerfeuer errichten</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2275,28 +2276,27 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Am Feuer ist Platz für mehr. Mit Pilzholz und Stein lässt sich das Lager ausbauen.</t>
+          <t>Dein Envoy braucht Steine und Pilzholz für das Lagerfeuer. Das kannst du immer in der Gegend sammeln.
+Aber Achtung: Alle Aktivitäten kosten den Envoy Energie. Achte also darauf, dass dein Envoy noch Energie übrig hat, um das Lagerfeuer zu errichten.
+Steigt die Ausdauer deines Envoy, steigt auch seine Energie.
+Sammle mit deinem Envoy 8 Steine und 2 Pilzholz, damit er ein Lagerfeuer errichten kann.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>kraft</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:6, stein:6</t>
+          <t>stein:8, pilzholz:2</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>freischaltung:zuhause, splitter:10</t>
+          <t>freischaltung:lagerfeuer</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -3364,19 +3364,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3392,42 +3386,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pilzholz</t>
+          <t>hygge_bis_naechste</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>stein</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>splitter</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>erholung</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>plaetze</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>schrank</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>beschreibung</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>datei_bild</t>
         </is>
       </c>
     </row>
@@ -3437,187 +3401,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Zelt</t>
+          <t>Lagerfeuer</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Eine Plane zwischen zwei Säulen, ein trockener Boden.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>stufe_1.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Steinhütte</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Vier Wände aus gestapeltem Stein und eine Tür, die schließt.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>stufe_2.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Baracke</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Lang, niedrig, warm. Platz für mehr als nur Schlaf.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>stufe_3.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Steinhaus</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Feste Mauern, Balken aus Pilzholz, ein Dach, das hält.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>stufe_4.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Turmhaus</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Ein Zimmer über dem anderen, oben ein Fenster in alle Richtungen.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>stufe_5.png</t>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Ein Feuer in einem Kreis aus Steinen. Es wärmt und hält die Dunkelheit auf Abstand.</t>
         </is>
       </c>
     </row>
@@ -3627,6 +3419,246 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>stufe</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>lagerstufe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pilzholz</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>stein</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>energie</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>kapazitaet</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>beschreibung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>steinlager</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Steinlager</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Eine Mulde, mit Pilzholz eingefasst. Hier liegen die Steine, bis sie gebraucht werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>pilzlager</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Pilzlager</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Ein Stapelplatz auf Latten, damit nichts im Boden fault.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>aufbewahrung</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Aufbewahrung</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Ein paar Fächer zwischen den Steinen. Was der Envoy nicht trägt, liegt hier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>schlafplatz</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Schlafplatz</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eine Fläche aus Pilzraspeln, weich genug für eine Nacht.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3712,7 +3744,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -3750,7 +3782,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -3788,7 +3820,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -3826,7 +3858,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -3864,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -3902,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -3940,7 +3972,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -3978,7 +4010,7 @@
         <v>60</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -4016,7 +4048,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -4054,7 +4086,7 @@
         <v>150</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -4092,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -4110,13 +4142,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4151,7 +4183,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung zum Lager bestimmt die Ausdauer für den Weg: 20 Einheiten Entfernung = 1 Ausdauer = 1 Minute.</t>
+          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung zum Lager bestimmt die Energie für den Weg: 20 Einheiten Entfernung = 1 Energie = 1 Minute.</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4195,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>lager (Ausgangspunkt jeder Expedition, dort steht das Zuhause), wild (Geister tauchen auf), sammeln (Pilzholz oder Stein), hoehle (mehrere Geister nacheinander), ort (feste Quests).</t>
+          <t>lager (Ausgangspunkt jeder Expedition, dort steht das Lager; Quests am Lager kosten keinen Weg), wild (Geister tauchen auf), sammeln (Pilzholz oder Stein), hoehle (mehrere Geister nacheinander), ort (feste Quests).</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4319,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Was nötig ist, um aufzubrechen: kraft&gt;=3, quest:q-spalt, summe_km&gt;=30, summe_stockwerke&gt;=100. Scheitern gibt es nicht.</t>
+          <t>Was nötig ist, um aufzubrechen: kraft&gt;=3, quest:q-spalt, summe_km&gt;=30, summe_stockwerke&gt;=100, lager&gt;=1 (Lagerstufe). Scheitern gibt es nicht.</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4331,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Ausdauer für die Arbeit vor Ort bei Werten auf 1. Jeder Punkt Ausdauer ist eine Minute: kosten 7 heißt 7 Minuten vor Ort. Hin- und Rückweg kommen nach Entfernung dazu.</t>
+          <t>Energie für die Arbeit vor Ort bei Werten auf 1. Jeder Punkt Energie ist eine Minute: kosten 7 heißt 7 Minuten vor Ort. Hin- und Rückweg kommen nach Entfernung dazu. Der Wert Ausdauer bestimmt die Energieleiste: 10 Energie je Level.</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4379,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:zuhause (Ausbau des Lagers) oder haendler, rast:1 (Leiste voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
+          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:lagerfeuer (Lager Stufe 1) oder haendler, rast:1 (Energie voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4410,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZUHAUSE</t>
+          <t>LAGERSTUFEN</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr"/>
@@ -4386,68 +4418,136 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pilzholz, stein, splitter</t>
+          <t>stufe, name</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Kosten für den Ausbau auf diese Stufe. Stufe 1 entsteht durch die Quest.</t>
+          <t>Stufe 1 entsteht mit dem Lagerfeuer (Quest q-lagerfeuer). Stufe 0 ist das Lager ohne Feuer und steht nicht in der Tabelle.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>erholung</t>
+          <t>hygge_bis_naechste</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Prozent schneller füllt sich die Ausdauerleiste.</t>
+          <t>Hygge, die das Lager braucht, bevor es auf die nächste Stufe ausgebaut werden kann. Hygge ist die Summe der Einrichtungen. Der Ausbau selbst folgt später.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>plaetze, schrank</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Plätze für Einrichtung, Fächer im Schrank.</t>
-        </is>
-      </c>
+          <t>EINRICHTUNGEN</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EINRICHTUNG</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr"/>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>steinlager, pilzlager, aufbewahrung, schlafplatz. Jede Einrichtung gibt es in Stufen; jede Zeile ist eine Stufe.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>effekt</t>
+          <t>lagerstufe</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>erholung:+5 und/oder glueck:+3 (Prozent).</t>
+          <t>Ab welcher Lagerstufe diese Stufe der Einrichtung errichtet werden kann.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>pilzholz, stein, energie</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Kosten: Material und Energie (zugleich Minuten), die das Errichten braucht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Wie viel Hygge diese Stufe zum Lager beiträgt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>kapazitaet</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Steinlager und Pilzlager: wie viele Stück sie fassen. Aufbewahrung: wie viele Plätze für Gegenstände.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Nur Schlafplatz: Prozent der Energieleiste, die der Envoy morgens zusätzlich hat (einmal am Tag, über den Rand hinaus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEKO</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>effekt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>erholung:+5 und/oder glueck:+3 (Prozent). Deko kommt erst mit Lagerstufe 2 ins Spiel; das Blatt ist vorbereitet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ab_stufe</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Ab welcher Stufe des Zuhauses sie aufgestellt werden kann.</t>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Ab welcher Lagerstufe sie aufgestellt werden kann.</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,12 +551,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>pilzhain</t>
+          <t>truemmerfeld</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Pilzhain</t>
+          <t>Trümmerfeld</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -565,14 +565,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>sammeln</t>
+          <t>truemmerfeld</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -584,19 +584,19 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Zwischen den Trümmern stehen Pilze, hoch wie Säulen. Ihre Stiele sind leicht und zäh.</t>
+          <t>Zwischen den umgestürzten Säulen liegen lose Steine und abgebrochene Pilzstiele, gleich beim Lager.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>steinbruch</t>
+          <t>pilzhain</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Alter Steinbruch</t>
+          <t>Pilzhain</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -624,19 +624,19 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Lose Blöcke, von niemandem vermisst.</t>
+          <t>Zwischen den Trümmern stehen Pilze, hoch wie Säulen. Ihre Stiele sind leicht und zäh.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>stillesufer</t>
+          <t>steinbruch</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Stilles Ufer</t>
+          <t>Alter Steinbruch</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -645,54 +645,50 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>sammeln</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>zauderling, gruebelkraehe</t>
-        </is>
-      </c>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Das Wasser steht still, als warte es.</t>
+          <t>Lose Blöcke, von niemandem vermisst.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>nebelfurt</t>
+          <t>stillesufer</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Nebelfurt</t>
+          <t>Stilles Ufer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nebelmark</t>
+          <t>Trümmerebene</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -706,25 +702,25 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>nebelwicht, zauderling, hastwind</t>
+          <t>zauderling, gruebelkraehe</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Wer hier übersetzt, sieht die eigene Hand nicht mehr.</t>
+          <t>Das Wasser steht still, als warte es.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>echohoehle</t>
+          <t>nebelfurt</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Echohöhle</t>
+          <t>Nebelfurt</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -733,38 +729,42 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>hoehle</t>
+          <t>wild</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>nebelwicht, zauderling, hastwind</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Jeder Schritt kommt dreimal zurück, jedes Mal etwas fremder.</t>
+          <t>Wer hier übersetzt, sieht die eigene Hand nicht mehr.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>spalt</t>
+          <t>echohoehle</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Der Spalt</t>
+          <t>Echohöhle</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -773,14 +773,14 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ort</t>
+          <t>hoehle</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,19 +792,19 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Zwei Felswände, kaum eine Schulter breit auseinander.</t>
+          <t>Jeder Schritt kommt dreimal zurück, jedes Mal etwas fremder.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>stillequelle</t>
+          <t>spalt</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Stille Quelle</t>
+          <t>Der Spalt</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -832,19 +832,19 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Ein Becken ohne Wellen. Man hört den eigenen Atem.</t>
+          <t>Zwei Felswände, kaum eine Schulter breit auseinander.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dornengrat</t>
+          <t>stillequelle</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Dornengrat</t>
+          <t>Stille Quelle</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -853,42 +853,38 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>dornenfluesterer, hastwind, gruebelkraehe</t>
-        </is>
-      </c>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Ein Grat aus schwarzen Splittern, der sich jeden Tag ein wenig schließt.</t>
+          <t>Ein Becken ohne Wellen. Man hört den eigenen Atem.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>mondsee</t>
+          <t>dornengrat</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Mondsee</t>
+          <t>Dornengrat</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -897,10 +893,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -914,113 +910,109 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>echo, nebelwicht, schwerer-schatten</t>
+          <t>dornenfluesterer, hastwind, gruebelkraehe</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Nachts spiegelt er Dinge, die nicht da sind.</t>
+          <t>Ein Grat aus schwarzen Splittern, der sich jeden Tag ein wenig schließt.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>schlucht</t>
+          <t>mondsee</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Die Schlucht</t>
+          <t>Mondsee</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Grenzland</t>
+          <t>Nebelmark</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ort</t>
+          <t>wild</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>echo, nebelwicht, schwerer-schatten</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Unten rauscht etwas. Von der alten Brücke hängen nur Ketten.</t>
+          <t>Nachts spiegelt er Dinge, die nicht da sind.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>aschenhang</t>
+          <t>schlucht</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Aschenhang</t>
+          <t>Die Schlucht</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Aschenland</t>
+          <t>Grenzland</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>schwerer-schatten, glutfresser, echo</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>quest:q-bruecke</t>
-        </is>
-      </c>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Grauer Staub, warm unter den Füßen. Weiter oben ein Thron.</t>
+          <t>Unten rauscht etwas. Von der alten Brücke hängen nur Ketten.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>turm</t>
+          <t>aschenhang</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Turm der Stufen</t>
+          <t>Aschenhang</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1029,22 +1021,26 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>ort</t>
+          <t>wild</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>schwerer-schatten, glutfresser, echo</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>quest:q-bruecke</t>
@@ -1052,31 +1048,31 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Niemand weiß, wie viele Stufen es sind. Man zählt beim Gehen.</t>
+          <t>Grauer Staub, warm unter den Füßen. Weiter oben ein Thron.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>langestrasse</t>
+          <t>turm</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Die lange Straße</t>
+          <t>Turm der Stufen</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Grenzland</t>
+          <t>Aschenland</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1096,53 +1092,97 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Gerade, gepflastert, ohne sichtbares Ende.</t>
+          <t>Niemand weiß, wie viele Stufen es sind. Man zählt beim Gehen.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>langestrasse</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Die lange Straße</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Grenzland</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ort</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>quest:q-bruecke</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Gerade, gepflastert, ohne sichtbares Ende.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>weisstal</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Weißes Tal</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Nordland</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D17" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>wild</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>nachtmahr, die-leere</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>quest:q-langestrasse</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Schnee, der nicht knirscht.</t>
         </is>
@@ -1151,7 +1191,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"lager,wild,sammeln,ort,hoehle"</formula1>
+      <formula1>"lager,truemmerfeld,wild,sammeln,ort,hoehle"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
@@ -4195,7 +4235,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>lager (Ausgangspunkt jeder Expedition, dort steht das Lager; Quests am Lager kosten keinen Weg), wild (Geister tauchen auf), sammeln (Pilzholz oder Stein), hoehle (mehrere Geister nacheinander), ort (feste Quests).</t>
+          <t>lager (Ausgangspunkt jeder Expedition, dort steht das Lager; Quests am Lager kosten keinen Weg), truemmerfeld (gleich beim Lager: dort sammelt der Envoy Stein und Pilzholz, ohne Weg; höchstens ein Ort), wild (Geister tauchen auf), sammeln (Pilzholz oder Stein), hoehle (mehrere Geister nacheinander), ort (feste Quests).</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>20</v>
@@ -3603,7 +3603,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>20</v>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Aufbewahrung</t>
+          <t>Krempelplatz</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -3642,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>6</v>
@@ -3681,7 +3681,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Hygge, die das Lager braucht, bevor es auf die nächste Stufe ausgebaut werden kann. Hygge ist die Summe der Einrichtungen. Der Ausbau selbst folgt später.</t>
+          <t>Hygge, ab der das Lager auf die nächste Stufe aufgewertet werden kann (kein Muss). Hygge ist die Summe der Einrichtungen, später auch der Deko. Jede Stufe verlangt mehr. Das Aufwerten selbst folgt später.</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>id, name</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>steinlager, pilzlager, aufbewahrung, schlafplatz. Jede Einrichtung gibt es in Stufen; jede Zeile ist eine Stufe.</t>
+          <t>id: steinlager, pilzlager, aufbewahrung, schlafplatz. Jede Einrichtung gibt es in Stufen; jede Zeile ist eine Stufe und kann ihren eigenen Namen haben (die Aufbewahrung heißt auf Stufe 1 Krempelplatz).</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -1961,7 +1961,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:1</t>
+          <t>pilzholz:7-9</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -2019,11 +2019,11 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:2-3</t>
+          <t>pilzholz:16-20</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -2085,11 +2085,11 @@
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:7-9</t>
+          <t>pilzholz:38-44</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>stein:1</t>
+          <t>stein:7-9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2205,11 +2205,11 @@
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>stein:2-3</t>
+          <t>stein:16-20</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2271,11 +2271,11 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>stein:7-9</t>
+          <t>stein:38-44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -544,7 +544,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Ein offener Platz auf dem Trümmerfeld, zwischen umgestürzten Säulen und hohen Pilzen. Hier beginnt und endet jeder Weg.</t>
+          <t>Ein offener Platz auf dem Trümmerfeld, zwischen umgestürzten Säulen und hohen Pilzen.</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -3704,7 +3704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3762,55 +3762,55 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>schlafmatte</t>
+          <t>wasserkrug</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Schlafmatte</t>
+          <t>Wasserkrug</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>erholung:+8</t>
+          <t>erholung:+4</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>haendler</t>
+          <t>haendler, beute</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Dick genug, um den Boden zu vergessen.</t>
+          <t>Immer kühl, immer gefüllt.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_schlafmatte.png</t>
+          <t>icon_einrichtung_wasserkrug.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>wasserkrug</t>
+          <t>kraeuterbund</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Wasserkrug</t>
+          <t>Kräuterbund</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>erholung:+4</t>
+          <t>erholung:+5</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3819,117 +3819,117 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Immer kühl, immer gefüllt.</t>
+          <t>Riecht nach einem Sommer, den es hier nie gab.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_wasserkrug.png</t>
+          <t>icon_einrichtung_kraeuterbund.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>kraeuterbund</t>
+          <t>laterne</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Kräuterbund</t>
+          <t>Laterne</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>erholung:+5</t>
+          <t>glueck:+3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>haendler, beute</t>
+          <t>haendler</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Riecht nach einem Sommer, den es hier nie gab.</t>
+          <t>Wirft ein ruhiges Licht.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_kraeuterbund.png</t>
+          <t>icon_einrichtung_laterne.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>laterne</t>
+          <t>windspiel</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Laterne</t>
+          <t>Windspiel</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>glueck:+3</t>
+          <t>glueck:+5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>haendler</t>
+          <t>beute, quest</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Wirft ein ruhiges Licht.</t>
+          <t>Klingt, bevor sich das Wetter ändert.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_laterne.png</t>
+          <t>icon_einrichtung_windspiel.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>windspiel</t>
+          <t>wolldecke</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Windspiel</t>
+          <t>Wolldecke</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>glueck:+5</t>
+          <t>erholung:+5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>beute, quest</t>
+          <t>beute</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -3940,67 +3940,67 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Klingt, bevor sich das Wetter ändert.</t>
+          <t>Schwer und warm.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_windspiel.png</t>
+          <t>icon_einrichtung_wolldecke.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>wolldecke</t>
+          <t>teppich</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Wolldecke</t>
+          <t>Teppich</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>erholung:+5</t>
+          <t>erholung:+6, glueck:+2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>beute</t>
+          <t>haendler</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Schwer und warm.</t>
+          <t>Muster, in denen man sich verlieren kann.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_wolldecke.png</t>
+          <t>icon_einrichtung_teppich.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>haengematte</t>
+          <t>regal</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Hängematte</t>
+          <t>Steinregal</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>erholung:+10</t>
+          <t>glueck:+4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4009,36 +4009,36 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Schaukelt noch, wenn man längst schläft.</t>
+          <t>Für alles, was man unterwegs findet.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_haengematte.png</t>
+          <t>icon_einrichtung_regal.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>teppich</t>
+          <t>kamin</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Teppich</t>
+          <t>Kamin</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>erholung:+6, glueck:+2</t>
+          <t>erholung:+15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4047,131 +4047,55 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Muster, in denen man sich verlieren kann.</t>
+          <t>Das Feuer zieht, der Rauch geht hinaus.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_teppich.png</t>
+          <t>icon_einrichtung_kamin.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>regal</t>
+          <t>splitterschale</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Steinregal</t>
+          <t>Splitterschale</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>glueck:+4</t>
+          <t>glueck:+8</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>haendler</t>
+          <t>quest</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Für alles, was man unterwegs findet.</t>
+          <t>Eine Schale voller Bannsplitter, die nie ganz erlöschen.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_regal.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>kamin</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Kamin</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>erholung:+15</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>haendler</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Das Feuer zieht, der Rauch geht hinaus.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_kamin.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>splitterschale</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Splitterschale</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>glueck:+8</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>quest</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Eine Schale voller Bannsplitter, die nie ganz erlöschen.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>icon_einrichtung_splitterschale.png</t>
         </is>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -3404,13 +3404,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3431,6 +3434,21 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>stein</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pilzholz</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>energie</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>beschreibung</t>
         </is>
       </c>
@@ -3441,15 +3459,124 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Lagerfeuer</t>
+          <t>Provisorisches Lager</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Ein Feuer in einem Kreis aus Steinen. Es wärmt und hält die Dunkelheit auf Abstand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Unterstand</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Ein schräges Dach aus Pilzholz und Pilzhut an einem Felsen, davor ein Windschutz aus Steinen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Wackelige Hütte</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Schiefe Wände aus Pilzholz, ein Dach aus Pilzhutstücken. Sie hält, meistens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Stabile Hütte</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Dieselbe Hütte, jetzt auf einem gemauerten Sockel. Drinnen bleibt es trocken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Steinhäuschen</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Gemauert, mit Tür, Fenster und Kamin.</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3548,7 +3675,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Steinlager</t>
+          <t>Steinstapel</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -3579,85 +3706,85 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>pilzlager</t>
+          <t>steinlager</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Pilzlager</t>
+          <t>Steinkiste</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" s="2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Ein Stapelplatz auf Latten, damit nichts im Boden fault.</t>
+          <t>Eine Kiste aus Pilzholz, mit Steinen beschwert, damit der Deckel hält.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>aufbewahrung</t>
+          <t>steinlager</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Krempelplatz</t>
+          <t>Steinschuppen</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Ein paar Fächer zwischen den Steinen. Was der Envoy nicht trägt, liegt hier.</t>
+          <t>Ein Schuppen neben dem Haus. Die Steine liegen trocken und sortiert.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>schlafplatz</t>
+          <t>pilzlager</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -3665,31 +3792,460 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Schlafplatz</t>
+          <t>Pilzholzstapel</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Ein Stapelplatz auf Latten, damit nichts im Boden fault.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>pilzlager</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Pilzholzgestell</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Ein Gestell aus Stielen, luftig, damit das Pilzholz trocknet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>pilzlager</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Pilzholzschuppen</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="E7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Ein Schuppen neben dem Haus, mit einem Dach aus Pilzhut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>aufbewahrung</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Krempelplatz</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Ein paar Fächer zwischen den Steinen. Was der Envoy nicht trägt, liegt hier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>aufbewahrung</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Kiste</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Eine Kiste mit Deckel. Was darin liegt, bleibt sauber.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>aufbewahrung</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Truhe</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Eine schwere Truhe mit Beschlägen aus Stein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>aufbewahrung</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Kleiderschrank</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="H11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Ein Schrank mit Türen und Fächern, für Kleidung und alles, was der Envoy findet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>schlafplatz</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Raspelnest</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>Eine Fläche aus Pilzraspeln, weich genug für eine Nacht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>schlafplatz</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Pilzmatte</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Eine Matte aus geflochtenen Pilzfasern, weicher als der Boden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>schlafplatz</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Schlafpodest</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Die Matte auf einem Sockel aus Steinen. Von unten wird es nicht mehr kalt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>schlafplatz</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Bett</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Ein Bett aus Pilzholz, mit einer Decke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>schlafplatz</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Himmelbett</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Ein Bett mit einem Dach aus Stoff. Darunter ist es still.</t>
         </is>
       </c>
     </row>
@@ -3704,17 +4260,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3730,30 +4290,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>effekt</t>
+          <t>lagerstufe</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>herkunft</t>
+          <t>hygge</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>fundort</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>seltenheit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>preis</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ab_stufe</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>pilzholz</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>stein</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>energie</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>beschreibung</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>datei_icon</t>
         </is>
@@ -3762,190 +4342,232 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>wasserkrug</t>
+          <t>pilzkappenschale</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Wasserkrug</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>erholung:+4</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>haendler, beute</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2" t="n">
+          <t>Pilzkappenschale</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Immer kühl, immer gefüllt.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_wasserkrug.png</t>
+      <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Eine flache Schale aus einem Pilzhut. Darin liegt, was der Envoy unterwegs aufhebt.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_pilzkappenschale.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>kraeuterbund</t>
+          <t>steinbank</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Kräuterbund</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>erholung:+5</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>haendler, beute</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+          <t>Steinbank</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Riecht nach einem Sommer, den es hier nie gab.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_kraeuterbund.png</t>
+      <c r="J3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Eine Bank aus flachen Steinen, gerade breit genug für zwei.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_steinbank.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>laterne</t>
+          <t>wasserkrug</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Laterne</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>glueck:+3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>haendler</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="n">
+          <t>Wasserkrug</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>stillesufer</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Wirft ein ruhiges Licht.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_laterne.png</t>
+      <c r="I4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Immer kühl, immer gefüllt.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_wasserkrug.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>windspiel</t>
+          <t>kraeuterbund</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Windspiel</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>glueck:+5</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>beute, quest</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+          <t>Kräuterbund</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>stillequelle</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Klingt, bevor sich das Wetter ändert.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_windspiel.png</t>
+      <c r="J5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Riecht nach einem Sommer, den es hier nie gab.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_kraeuterbund.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>wolldecke</t>
+          <t>windspiel</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Wolldecke</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>erholung:+5</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>beute</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Schwer und warm.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_wolldecke.png</t>
+          <t>Windspiel</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>geister</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Klingt, bevor sich das Wetter ändert.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_windspiel.png</t>
         </is>
       </c>
     </row>
@@ -3960,28 +4582,40 @@
           <t>Teppich</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>erholung:+6, glueck:+2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>haendler</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Muster, in denen man sich verlieren kann.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>icon_einrichtung_teppich.png</t>
         </is>
@@ -3990,118 +4624,487 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>regal</t>
+          <t>kamin</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Steinregal</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>glueck:+4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>haendler</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Für alles, was man unterwegs findet.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_regal.png</t>
+          <t>Kamin</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Das Feuer zieht, der Rauch geht hinaus.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_kamin.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>kamin</t>
+          <t>laterne</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Kamin</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>erholung:+15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>haendler</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="F9" s="2" t="n">
+          <t>Laterne</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Das Feuer zieht, der Rauch geht hinaus.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>icon_einrichtung_kamin.png</t>
+      <c r="D9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>langestrasse</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Wirft ein ruhiges Licht.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_laterne.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>leuchtmooskasten</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Leuchtmooskasten</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>pilzhain</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Ein Kasten voll Moos, das nachts leise leuchtet.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_leuchtmooskasten.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>pilzholztisch</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pilzholztisch</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>haendler</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Ein Tisch aus einem einzigen Pilzstiel.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_pilzholztisch.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>regal</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Steinregal</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>steinbruch</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Für alles, was man unterwegs findet.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_regal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>wandbehang</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Wandbehang</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>q-furtwache</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Ein Tuch mit einem Muster aus Nebel und Wasser.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_wandbehang.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>nebelspiegel</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Nebelspiegel</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>mondsee</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>kostbar</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Ein Spiegel, in dem der Nebel stillsteht.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_nebelspiegel.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>sternkarte</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sternkarte</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>q-mondnacht</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Die Sterne über dem Mondsee, Punkt für Punkt.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_sternkarte.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>klangschale</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Klangschale</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>echohoehle</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Ein Schlag, und der Ton bleibt lange im Raum.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_klangschale.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>splitterschale</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Splitterschale</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>glueck:+8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>quest</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="D17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>geister</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>kostbar</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Eine Schale voller Bannsplitter, die nie ganz erlöschen.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>icon_einrichtung_splitterschale.png</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"selten,sehr selten,kostbar"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4112,7 +5115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4343,7 +5346,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, einrichtung:&lt;id&gt;, freischaltung:lagerfeuer (Lager Stufe 1) oder haendler, rast:1 (Energie voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
+          <t>splitter:20, pilzholz:2-4, stein:1-3, item:&lt;id&gt;, plan:&lt;id&gt; (Plan einer Deko, sicher), freischaltung:lagerfeuer (Lager Stufe 1) oder haendler, rast:1 (Energie voll). Bei Höhlen nur, wenn alle Geister bezwungen sind.</t>
         </is>
       </c>
     </row>
@@ -4399,119 +5402,215 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Hygge, ab der das Lager auf die nächste Stufe aufgewertet werden kann (kein Muss). Hygge ist die Summe der Einrichtungen, später auch der Deko. Jede Stufe verlangt mehr. Das Aufwerten selbst folgt später.</t>
+          <t>Hygge, ab der das Lager auf die nächste Stufe aufgewertet werden kann (kein Muss). Hygge ist die Summe der Einrichtungen und der gebauten Deko. Leer auf der letzten Stufe.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EINRICHTUNGEN</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr"/>
+          <t>stein, pilzholz, energie</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Was das Aufwerten von dieser Stufe auf die nächste kostet. Die Energie wird am Stück gebraucht, die Leiste muss also groß genug sein.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>id, name</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>id: steinlager, pilzlager, aufbewahrung, schlafplatz. Jede Einrichtung gibt es in Stufen; jede Zeile ist eine Stufe und kann ihren eigenen Namen haben (die Aufbewahrung heißt auf Stufe 1 Krempelplatz).</t>
-        </is>
-      </c>
+          <t>EINRICHTUNGEN</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lagerstufe</t>
+          <t>id, name</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Ab welcher Lagerstufe diese Stufe der Einrichtung errichtet werden kann.</t>
+          <t>id: steinlager, pilzlager, aufbewahrung, schlafplatz. Jede Einrichtung gibt es in Stufen; jede Zeile ist eine Stufe mit eigenem Namen.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pilzholz, stein, energie</t>
+          <t>lagerstufe</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Kosten: Material und Energie (zugleich Minuten), die das Errichten braucht.</t>
+          <t>Ab welcher Lagerstufe diese Stufe der Einrichtung gebaut werden kann.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hygge</t>
+          <t>pilzholz, stein, energie</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Wie viel Hygge diese Stufe zum Lager beiträgt.</t>
+          <t>Kosten: Material und Energie (zugleich Minuten), die der Bau braucht.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kapazitaet</t>
+          <t>hygge</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Steinlager und Pilzlager: wie viele Stück sie fassen. Aufbewahrung: wie viele Plätze für Gegenstände.</t>
+          <t>Wie viel Hygge die Einrichtung auf dieser Stufe zum Lager beiträgt (nicht zusätzlich zur Stufe davor).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>kapazitaet</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Nur Schlafplatz: Prozent der Energieleiste, die der Envoy morgens zusätzlich hat (einmal am Tag, über den Rand hinaus).</t>
+          <t>Steinlager und Pilzlager: wie viele Stück sie fassen. Aufbewahrung: wie viele Plätze für Gegenstände.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEKO</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr"/>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Nur Schlafplatz: Prozent der Energieleiste, die der Envoy morgens zusätzlich hat (einmal am Tag, über den Rand hinaus).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>effekt</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>erholung:+5 und/oder glueck:+3 (Prozent). Deko kommt erst mit Lagerstufe 2 ins Spiel; das Blatt ist vorbereitet.</t>
+          <t>Optional: assets/lager/einrichtung_&lt;id&gt;_&lt;stufe&gt;.png, 1792 × 672, transparent, an ihrem Platz im Lagerbild gezeichnet. Ohne Bild erscheint sie nicht im Lagerbild.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ab_stufe</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Ab welcher Lagerstufe sie aufgestellt werden kann.</t>
+          <t>DEKO</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>lagerstufe</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Ab welcher Lagerstufe die Deko in der Liste steht und gebaut werden kann (ab 2). Deko bleibt beim Aufwerten stehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Wie viel Hygge sie gibt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fundort</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Woher der Plan kommt: start (gleich da, sobald die Lagerstufe erreicht ist), eine Orts-id (jede Aktion dort zählt als Suche), eine Quest-id (nur diese Quest; sie sollte wiederholbar sein), geister (jeder Geist, dem der Envoy begegnet) oder haendler (liegt an manchen Tagen beim Händler).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>seltenheit</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>selten, sehr selten oder kostbar. Gesucht wird erst ab der Lagerstufe der Deko. Je 10 Minuten am Fundort, je Geist oder je Tag beim Händler ist eine Chance. Im Schnitt braucht ein seltener Plan 6 Chancen, ein sehr seltener 12, ein kostbarer 24. Spätestens nach doppelt so vielen ist er sicher da.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>preis</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Nur beim Händler: was der Plan dort kostet, in Bannsplittern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>pilzholz, stein, energie</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Was der Bau kostet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>datei_icon</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Icon in assets/icons/, 256 × 256, PNG mit Alphakanal. Leer = icon_einrichtung_&lt;id&gt;.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Optional: assets/lager/deko_&lt;id&gt;.png, 1792 × 672, transparent, an ihrem Platz im Lagerbild gezeichnet.</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -3714,7 +3714,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Steinkiste</t>
+          <t>Steinpferch</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -3738,7 +3738,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Eine Kiste aus Pilzholz, mit Steinen beschwert, damit der Deckel hält.</t>
+          <t>Ein Pferch aus Pilzholzstielen, damit der Haufen nicht auseinanderrollt.</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -3089,7 +3089,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>summe_stockwerke&gt;=100</t>
+          <t>summe_treppe_min&gt;=60</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -3149,13 +3149,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Die Straße endet nur für die, die schon viele Kilometer in den Beinen haben.</t>
+          <t>Die Straße endet nur für die, die schon viele Stufen in den Beinen haben.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>summe_km&gt;=30</t>
+          <t>summe_treppe_min&gt;=150</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Was nötig ist, um aufzubrechen: kraft&gt;=3, quest:q-spalt, summe_km&gt;=30, summe_stockwerke&gt;=100, lager&gt;=1 (Lagerstufe). Scheitern gibt es nicht.</t>
+          <t>Was nötig ist, um aufzubrechen: kraft&gt;=3, quest:q-spalt, summe_treppe_min&gt;=60 (Minuten Treppe im Tageswerk, insgesamt), lager&gt;=1 (Lagerstufe). Scheitern gibt es nicht.</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -1818,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2357,17 +2357,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>q-uferkies</t>
+          <t>q-handwickel</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Splitter im Uferkies</t>
+          <t>Stoff zwischen den Trümmern</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>stillesufer</t>
+          <t>truemmerfeld</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2377,29 +2377,25 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Wo früher Geister gebannt wurden, glimmen noch Splitter zwischen den Kieseln.</t>
+          <t>Unter einer umgestürzten Säule klemmt ein langer Streifen Leinen. Um die Hände gewickelt, schützt er die Knöchel.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>splitter:1</t>
+          <t>item:handschuhe_handwickel_1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N9" s="2" t="n">
@@ -2415,12 +2411,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>q-saeule</t>
+          <t>q-uferkies</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Die umgestürzte Säule</t>
+          <t>Splitter im Uferkies</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2435,32 +2431,24 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Eine Säule liegt quer über dem Pfad. Wer sie zerlegt, hat Stein für Tage.</t>
+          <t>Wo früher Geister gebannt wurden, glimmen noch Splitter zwischen den Kieseln.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>kraft&gt;=3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>kraft</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>kraft</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>stein:4-6, splitter:4</t>
+          <t>splitter:1</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -2469,7 +2457,7 @@
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -2481,57 +2469,61 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>q-haendler</t>
+          <t>q-saeule</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Der Händler im Nebel</t>
+          <t>Die umgestürzte Säule</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>nebelfurt</t>
+          <t>stillesufer</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>In der Furt ruft jemand um Hilfe. Ein Wagen steckt fest, und davor steht etwas Großes.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>nebelwaechter</t>
-        </is>
-      </c>
+          <t>Eine Säule liegt quer über dem Pfad. Wer sie zerlegt, hat Stein für Tage.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=3, ausdauer&gt;=3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>kraft&gt;=3</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>freischaltung:haendler, splitter:25</t>
+          <t>stein:4-6, splitter:4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -2543,12 +2535,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>q-furtwache</t>
+          <t>q-haendler</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Wache an der Furt</t>
+          <t>Der Händler im Nebel</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2558,46 +2550,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>kampf</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Lange am Wasser sitzen, bis der Nebel zeigt, was er mit sich trägt.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>In der Furt ruft jemand um Hilfe. Ein Wagen steckt fest, und davor steht etwas Großes.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>nebelwaechter</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=5</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
+          <t>kraft&gt;=3, ausdauer&gt;=3</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>splitter:9-12</t>
+          <t>freischaltung:haendler, splitter:25</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2609,48 +2597,52 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>q-echohoehle</t>
+          <t>q-furtwache</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Die Echohöhle</t>
+          <t>Wache an der Furt</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>echohoehle</t>
+          <t>nebelfurt</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>hoehle</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an den Werten.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>zauderling, nebelwicht, gruebelkraehe, hastwind, dornenfluesterer</t>
-        </is>
-      </c>
+          <t>Lange am Wasser sitzen, bis der Nebel zeigt, was er mit sich trägt.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>gelassenheit&gt;=5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>splitter:30, item:beine_kampfhose_2</t>
+          <t>splitter:9-12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -2659,7 +2651,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -2671,61 +2663,57 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>q-spalt</t>
+          <t>q-echohoehle</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Durch den Spalt</t>
+          <t>Die Echohöhle</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>spalt</t>
+          <t>echohoehle</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>hoehle</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an den Werten.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>zauderling, nebelwicht, gruebelkraehe, hastwind, dornenfluesterer</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit&gt;=4</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>beweglichkeit</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>beweglichkeit</t>
-        </is>
-      </c>
+          <t>kraft&gt;=2</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>splitter:15, item:kopf_stirnband_1</t>
+          <t>splitter:30, item:beine_kampfhose_2</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2737,17 +2725,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>q-quelle</t>
+          <t>q-spalt</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Die stille Quelle</t>
+          <t>Durch den Spalt</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>stillequelle</t>
+          <t>spalt</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2757,41 +2745,41 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
+          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=3</t>
+          <t>beweglichkeit&gt;=4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit</t>
+          <t>beweglichkeit</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit</t>
+          <t>beweglichkeit</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>splitter:8, rast:1</t>
+          <t>splitter:15, item:kopf_stirnband_1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -2803,17 +2791,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>q-dornen</t>
+          <t>q-quelle</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Über den Dornengrat</t>
+          <t>Die stille Quelle</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>dornengrat</t>
+          <t>stillequelle</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2823,18 +2811,18 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Der Grat flüstert. Hinüber kommt, wer sich weder hetzen noch festhalten lässt.</t>
+          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit&gt;=5, gelassenheit&gt;=4</t>
+          <t>gelassenheit&gt;=3</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2844,20 +2832,20 @@
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>splitter:20</t>
+          <t>splitter:8, rast:1</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2869,52 +2857,52 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>q-bruecke</t>
+          <t>q-dornen</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Die Brücke über die Schlucht</t>
+          <t>Über den Dornengrat</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>schlucht</t>
+          <t>dornengrat</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>bauen</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Mit Pilzholz, Stein und einem langen Atem lässt sich die Brücke neu legen.</t>
+          <t>Der Grat flüstert. Hinüber kommt, wer sich weder hetzen noch festhalten lässt.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ausdauer&gt;=5, kraft&gt;=4</t>
+          <t>beweglichkeit&gt;=5, gelassenheit&gt;=4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>kraft, ausdauer</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>pilzholz:10, stein:12</t>
-        </is>
-      </c>
+          <t>beweglichkeit</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>splitter:30, item:handschuhe_griffhandschuhe_2</t>
+          <t>splitter:20</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2935,48 +2923,52 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>q-mondsee</t>
+          <t>q-bruecke</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Spiegel im Mondsee</t>
+          <t>Die Brücke über die Schlucht</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>mondsee</t>
+          <t>schlucht</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>bauen</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>echo</t>
-        </is>
-      </c>
+          <t>Mit Pilzholz, Stein und einem langen Atem lässt sich die Brücke neu legen.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=6</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>ausdauer&gt;=5, kraft&gt;=4</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>pilzholz:10, stein:12</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>splitter:35, item:kopf_stillemaske_3</t>
+          <t>splitter:30, item:handschuhe_griffhandschuhe_2</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2997,12 +2989,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>q-mondnacht</t>
+          <t>q-mondsee</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Eine Nacht am Mondsee</t>
+          <t>Spiegel im Mondsee</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3012,46 +3004,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>kampf</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Bis der Mond über das Wasser gewandert ist. Was dann im Uferschlamm liegt, hat lange gewartet.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>echo</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>quest:q-mondsee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
+          <t>gelassenheit&gt;=6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>splitter:15-19</t>
+          <t>splitter:35, item:kopf_stillemaske_3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -3063,17 +3051,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>q-turm</t>
+          <t>q-mondnacht</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Der Turm der Stufen</t>
+          <t>Eine Nacht am Mondsee</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>turm</t>
+          <t>mondsee</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3083,41 +3071,41 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
+          <t>Bis der Mond über das Wasser gewandert ist. Was dann im Uferschlamm liegt, hat lange gewartet.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>summe_treppe_min&gt;=60</t>
+          <t>quest:q-mondsee</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>ausdauer</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>ausdauer</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
+          <t>splitter:15-19</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -3129,17 +3117,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>q-langestrasse</t>
+          <t>q-turm</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Die lange Straße</t>
+          <t>Der Turm der Stufen</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>langestrasse</t>
+          <t>turm</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3149,13 +3137,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Die Straße endet nur für die, die schon viele Stufen in den Beinen haben.</t>
+          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>summe_treppe_min&gt;=150</t>
+          <t>summe_treppe_min&gt;=60</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3170,11 +3158,11 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>splitter:40</t>
+          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3195,12 +3183,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>q-horizont</t>
+          <t>q-langestrasse</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Bis zum Horizont</t>
+          <t>Die lange Straße</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3215,13 +3203,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Hinter dem Ende der Straße geht es weiter. Wer bis zum Abend läuft, kommt mit vollen Taschen zurück.</t>
+          <t>Die Straße endet nur für die, die schon viele Stufen in den Beinen haben.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>quest:q-langestrasse</t>
+          <t>summe_treppe_min&gt;=150</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3236,20 +3224,20 @@
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>splitter:24-30</t>
+          <t>splitter:40</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -3261,57 +3249,61 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>q-aschenthron</t>
+          <t>q-horizont</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Der Aschenthron</t>
+          <t>Bis zum Horizont</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>aschenhang</t>
+          <t>langestrasse</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>hoehle</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Der Weg zum Thron führt an drei Wächtern vorbei. Oben sitzt sie, auf kalter Glut.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>schwerer-schatten, glutfresser, glutfresser, aschenkoenigin</t>
-        </is>
-      </c>
+          <t>Hinter dem Ende der Straße geht es weiter. Wer bis zum Abend läuft, kommt mit vollen Taschen zurück.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=8</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>quest:q-langestrasse</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>splitter:120, item:handschuhe_nebelwickel_4</t>
+          <t>splitter:24-30</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -3323,48 +3315,48 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>q-leere</t>
+          <t>q-aschenthron</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Das weiße Schweigen</t>
+          <t>Der Aschenthron</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>weisstal</t>
+          <t>aschenhang</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>hoehle</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Im Tal wartet etwas, das man nicht besiegen muss.</t>
+          <t>Der Weg zum Thron führt an drei Wächtern vorbei. Oben sitzt sie, auf kalter Glut.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>die-leere</t>
+          <t>schwerer-schatten, glutfresser, glutfresser, aschenkoenigin</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=10</t>
+          <t>kraft&gt;=8</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>splitter:200</t>
+          <t>splitter:120, item:handschuhe_nebelwickel_4</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3381,6 +3373,68 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>q-leere</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Das weiße Schweigen</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>weisstal</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>kampf</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Im Tal wartet etwas, das man nicht besiegen muss.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>die-leere</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit&gt;=10</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>splitter:200</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -1818,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1924,12 +1924,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>q-pilzholz-klein</t>
+          <t>q-bastsandalen</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pilzholz auflesen</t>
+          <t>Bast aus dem Pilzhain</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1939,34 +1939,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>sammeln</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Was der Wind von den Hüten gebrochen hat, liegt leicht im Moos.</t>
+          <t>Die alten Pilzstiele lassen lange, zähe Fasern los. Geflochten und um die Füße gebunden, tragen sie über Stein und Splitter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>kraft</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:7-9</t>
+          <t>item:schuhe_bastsandalen_1</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -1982,12 +1978,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>q-pilzholz</t>
+          <t>q-pilzholz-klein</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Pilzholz schlagen</t>
+          <t>Pilzholz auflesen</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2002,16 +1998,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Einen Stiel fällen und in leichte, handliche Stücke teilen.</t>
+          <t>Was der Wind von den Hüten gebrochen hat, liegt leicht im Moos.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>kraft, ausdauer</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>kraft</t>
@@ -2019,11 +2011,11 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:16-20</t>
+          <t>pilzholz:7-9</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -2044,12 +2036,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>q-pilzholz-gross</t>
+          <t>q-pilzholz</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Einen Riesenpilz fällen</t>
+          <t>Pilzholz schlagen</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2064,15 +2056,11 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Ein ganzer Stamm, so hoch wie eine Säule. Das Holz reicht für eine Wand.</t>
+          <t>Einen Stiel fällen und in leichte, handliche Stücke teilen.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>kraft&gt;=4</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>kraft, ausdauer</t>
@@ -2085,11 +2073,11 @@
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:38-44</t>
+          <t>pilzholz:16-20</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2110,17 +2098,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>q-stein-klein</t>
+          <t>q-pilzholz-gross</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Lose Steine auflesen</t>
+          <t>Einen Riesenpilz fällen</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>steinbruch</t>
+          <t>pilzhain</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2130,12 +2118,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Am Rand des Bruchs liegt, was von allein herabgefallen ist.</t>
+          <t>Ein ganzer Stamm, so hoch wie eine Säule. Das Holz reicht für eine Wand.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=4</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>kraft</t>
@@ -2143,11 +2139,11 @@
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>stein:7-9</t>
+          <t>pilzholz:38-44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2168,12 +2164,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>q-stein</t>
+          <t>q-stein-klein</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Steine brechen</t>
+          <t>Lose Steine auflesen</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2188,16 +2184,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Lose Blöcke lösen und handlich schlagen.</t>
+          <t>Am Rand des Bruchs liegt, was von allein herabgefallen ist.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>kraft</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>kraft</t>
@@ -2205,11 +2197,11 @@
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>stein:16-20</t>
+          <t>stein:7-9</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2230,12 +2222,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>q-stein-gross</t>
+          <t>q-stein</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Einen Block lösen</t>
+          <t>Steine brechen</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2250,15 +2242,11 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Ein Block aus der Wand, sauber gespalten. Schwer, aber er trägt ein Haus.</t>
+          <t>Lose Blöcke lösen und handlich schlagen.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>kraft&gt;=5</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>kraft</t>
@@ -2271,11 +2259,11 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>stein:38-44</t>
+          <t>stein:16-20</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2296,25 +2284,91 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>q-stein-gross</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Einen Block lösen</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>steinbruch</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sammeln</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Ein Block aus der Wand, sauber gespalten. Schwer, aber er trägt ein Haus.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=5</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>stein:38-44</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>q-lagerfeuer</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Ein Lagerfeuer errichten</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>lager</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>bauen</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Dein Envoy braucht Steine und Pilzholz für das Lagerfeuer. Das kannst du immer in der Gegend sammeln.
 Aber Achtung: Alle Aktivitäten kosten den Envoy Energie. Achte also darauf, dass dein Envoy noch Energie übrig hat, um das Lagerfeuer zu errichten.
@@ -2322,75 +2376,21 @@
 Sammle mit deinem Envoy 8 Steine und 2 Pilzholz, damit er ein Lagerfeuer errichten kann.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>stein:8, pilzholz:2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>freischaltung:lagerfeuer</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>q-handwickel</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Stoff zwischen den Trümmern</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>truemmerfeld</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>erkunden</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Unter einer umgestürzten Säule klemmt ein langer Streifen Leinen. Um die Hände gewickelt, schützt er die Knöchel.</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>stein:8, pilzholz:2</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>item:handschuhe_handwickel_1</t>
+          <t>freischaltung:lagerfeuer</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2411,17 +2411,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>q-uferkies</t>
+          <t>q-handwickel</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Splitter im Uferkies</t>
+          <t>Stoff zwischen den Trümmern</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>stillesufer</t>
+          <t>truemmerfeld</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2431,29 +2431,25 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Wo früher Geister gebannt wurden, glimmen noch Splitter zwischen den Kieseln.</t>
+          <t>Unter einer umgestürzten Säule klemmt ein langer Streifen Leinen. Um die Hände gewickelt, schützt er die Knöchel.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>splitter:1</t>
+          <t>item:handschuhe_handwickel_1</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N10" s="2" t="n">
@@ -2469,12 +2465,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>q-saeule</t>
+          <t>q-uferkies</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Die umgestürzte Säule</t>
+          <t>Splitter im Uferkies</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2489,32 +2485,24 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Eine Säule liegt quer über dem Pfad. Wer sie zerlegt, hat Stein für Tage.</t>
+          <t>Wo früher Geister gebannt wurden, glimmen noch Splitter zwischen den Kieseln.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>kraft&gt;=3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>kraft</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>kraft</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>stein:4-6, splitter:4</t>
+          <t>splitter:1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -2523,7 +2511,7 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -2535,57 +2523,61 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>q-haendler</t>
+          <t>q-saeule</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Der Händler im Nebel</t>
+          <t>Die umgestürzte Säule</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>nebelfurt</t>
+          <t>stillesufer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>In der Furt ruft jemand um Hilfe. Ein Wagen steckt fest, und davor steht etwas Großes.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>nebelwaechter</t>
-        </is>
-      </c>
+          <t>Eine Säule liegt quer über dem Pfad. Wer sie zerlegt, hat Stein für Tage.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=3, ausdauer&gt;=3</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>kraft&gt;=3</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>kraft</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>freischaltung:haendler, splitter:25</t>
+          <t>stein:4-6, splitter:4</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2597,12 +2589,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>q-furtwache</t>
+          <t>q-haendler</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Wache an der Furt</t>
+          <t>Der Händler im Nebel</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2612,46 +2604,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>kampf</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Lange am Wasser sitzen, bis der Nebel zeigt, was er mit sich trägt.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>In der Furt ruft jemand um Hilfe. Ein Wagen steckt fest, und davor steht etwas Großes.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>nebelwaechter</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
+          <t>kraft&gt;=3, ausdauer&gt;=3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>splitter:9-12</t>
+          <t>freischaltung:haendler, splitter:25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -2663,48 +2651,52 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>q-echohoehle</t>
+          <t>q-furtwache</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Die Echohöhle</t>
+          <t>Wache an der Furt</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>echohoehle</t>
+          <t>nebelfurt</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>hoehle</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an den Werten.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>zauderling, nebelwicht, gruebelkraehe, hastwind, dornenfluesterer</t>
-        </is>
-      </c>
+          <t>Lange am Wasser sitzen, bis der Nebel zeigt, was er mit sich trägt.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=2</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>gelassenheit&gt;=5</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>splitter:30, item:beine_kampfhose_2</t>
+          <t>splitter:9-12</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2713,7 +2705,7 @@
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -2725,61 +2717,57 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>q-spalt</t>
+          <t>q-echohoehle</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Durch den Spalt</t>
+          <t>Die Echohöhle</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>spalt</t>
+          <t>echohoehle</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>hoehle</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>Tief drinnen hausen fünf Geister. Wie weit der Envoy kommt, hängt an den Werten.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>zauderling, nebelwicht, gruebelkraehe, hastwind, dornenfluesterer</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit&gt;=4</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>beweglichkeit</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>beweglichkeit</t>
-        </is>
-      </c>
+          <t>kraft&gt;=2</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="n">
         <v>12</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>splitter:15, item:kopf_stirnband_1</t>
+          <t>splitter:30, item:beine_kampfhose_2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -2791,17 +2779,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>q-quelle</t>
+          <t>q-spalt</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Die stille Quelle</t>
+          <t>Durch den Spalt</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>stillequelle</t>
+          <t>spalt</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2811,41 +2799,41 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
+          <t>Dahinter soll ein Versteck liegen. Hindurch passt nur, wer sich drehen und strecken kann.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=3</t>
+          <t>beweglichkeit&gt;=4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit</t>
+          <t>beweglichkeit</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit</t>
+          <t>beweglichkeit</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>splitter:8, rast:1</t>
+          <t>splitter:15, item:kopf_stirnband_1</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2857,17 +2845,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>q-dornen</t>
+          <t>q-quelle</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Über den Dornengrat</t>
+          <t>Die stille Quelle</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>dornengrat</t>
+          <t>stillequelle</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2877,18 +2865,18 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Der Grat flüstert. Hinüber kommt, wer sich weder hetzen noch festhalten lässt.</t>
+          <t>Wer am Rand sitzen bleibt, bis das Wasser ganz ruhig ist, steht erholt wieder auf.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit&gt;=5, gelassenheit&gt;=4</t>
+          <t>gelassenheit&gt;=3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>beweglichkeit</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2898,20 +2886,20 @@
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>splitter:20</t>
+          <t>splitter:8, rast:1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -2923,52 +2911,52 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>q-bruecke</t>
+          <t>q-dornen</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Die Brücke über die Schlucht</t>
+          <t>Über den Dornengrat</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>schlucht</t>
+          <t>dornengrat</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>bauen</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Mit Pilzholz, Stein und einem langen Atem lässt sich die Brücke neu legen.</t>
+          <t>Der Grat flüstert. Hinüber kommt, wer sich weder hetzen noch festhalten lässt.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ausdauer&gt;=5, kraft&gt;=4</t>
+          <t>beweglichkeit&gt;=5, gelassenheit&gt;=4</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>kraft, ausdauer</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>pilzholz:10, stein:12</t>
-        </is>
-      </c>
+          <t>beweglichkeit</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>splitter:30, item:handschuhe_griffhandschuhe_2</t>
+          <t>splitter:20</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2989,48 +2977,52 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>q-mondsee</t>
+          <t>q-bruecke</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Spiegel im Mondsee</t>
+          <t>Die Brücke über die Schlucht</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>mondsee</t>
+          <t>schlucht</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>bauen</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>echo</t>
-        </is>
-      </c>
+          <t>Mit Pilzholz, Stein und einem langen Atem lässt sich die Brücke neu legen.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=6</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>ausdauer&gt;=5, kraft&gt;=4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>kraft, ausdauer</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>pilzholz:10, stein:12</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>splitter:35, item:kopf_stillemaske_3</t>
+          <t>splitter:30, item:handschuhe_griffhandschuhe_2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -3051,12 +3043,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>q-mondnacht</t>
+          <t>q-mondsee</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Eine Nacht am Mondsee</t>
+          <t>Spiegel im Mondsee</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3066,46 +3058,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>erkunden</t>
+          <t>kampf</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Bis der Mond über das Wasser gewandert ist. Was dann im Uferschlamm liegt, hat lange gewartet.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>Im Wasser steht jemand, der nur wiederholt, was man selbst einmal gesagt hat.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>echo</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>quest:q-mondsee</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>gelassenheit</t>
-        </is>
-      </c>
+          <t>gelassenheit&gt;=6</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>splitter:15-19</t>
+          <t>splitter:35, item:kopf_stillemaske_3</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -3117,17 +3105,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>q-turm</t>
+          <t>q-mondnacht</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Der Turm der Stufen</t>
+          <t>Eine Nacht am Mondsee</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>turm</t>
+          <t>mondsee</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3137,41 +3125,41 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
+          <t>Bis der Mond über das Wasser gewandert ist. Was dann im Uferschlamm liegt, hat lange gewartet.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>summe_treppe_min&gt;=60</t>
+          <t>quest:q-mondsee</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>ausdauer</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>ausdauer</t>
+          <t>gelassenheit</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
+          <t>splitter:15-19</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -3183,17 +3171,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>q-langestrasse</t>
+          <t>q-turm</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Die lange Straße</t>
+          <t>Der Turm der Stufen</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>langestrasse</t>
+          <t>turm</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3203,13 +3191,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Die Straße endet nur für die, die schon viele Stufen in den Beinen haben.</t>
+          <t>Oben soll man weit sehen. Wer im echten Leben genug Stufen gegangen ist, kennt den Rhythmus.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>summe_treppe_min&gt;=150</t>
+          <t>summe_treppe_min&gt;=60</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3224,11 +3212,11 @@
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>splitter:40</t>
+          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3249,12 +3237,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>q-horizont</t>
+          <t>q-langestrasse</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Bis zum Horizont</t>
+          <t>Die lange Straße</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3269,13 +3257,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Hinter dem Ende der Straße geht es weiter. Wer bis zum Abend läuft, kommt mit vollen Taschen zurück.</t>
+          <t>Die Straße endet nur für die, die schon viele Stufen in den Beinen haben.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>quest:q-langestrasse</t>
+          <t>summe_treppe_min&gt;=150</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3290,20 +3278,20 @@
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>splitter:24-30</t>
+          <t>splitter:40</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -3315,57 +3303,61 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>q-aschenthron</t>
+          <t>q-horizont</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Der Aschenthron</t>
+          <t>Bis zum Horizont</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>aschenhang</t>
+          <t>langestrasse</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>hoehle</t>
+          <t>erkunden</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Der Weg zum Thron führt an drei Wächtern vorbei. Oben sitzt sie, auf kalter Glut.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>schwerer-schatten, glutfresser, glutfresser, aschenkoenigin</t>
-        </is>
-      </c>
+          <t>Hinter dem Ende der Straße geht es weiter. Wer bis zum Abend läuft, kommt mit vollen Taschen zurück.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=8</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>quest:q-langestrasse</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>ausdauer</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>splitter:120, item:handschuhe_nebelwickel_4</t>
+          <t>splitter:24-30</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3377,48 +3369,48 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>q-leere</t>
+          <t>q-aschenthron</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Das weiße Schweigen</t>
+          <t>Der Aschenthron</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>weisstal</t>
+          <t>aschenhang</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>kampf</t>
+          <t>hoehle</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Im Tal wartet etwas, das man nicht besiegen muss.</t>
+          <t>Der Weg zum Thron führt an drei Wächtern vorbei. Oben sitzt sie, auf kalter Glut.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>die-leere</t>
+          <t>schwerer-schatten, glutfresser, glutfresser, aschenkoenigin</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>gelassenheit&gt;=10</t>
+          <t>kraft&gt;=8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>splitter:200</t>
+          <t>splitter:120, item:handschuhe_nebelwickel_4</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3435,6 +3427,68 @@
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>q-leere</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Das weiße Schweigen</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>weisstal</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>kampf</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Im Tal wartet etwas, das man nicht besiegen muss.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>die-leere</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>gelassenheit&gt;=10</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>splitter:200</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>splitter:1</t>
+          <t>splitter:3-4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>stein:4-6, splitter:4</t>
+          <t>stein:4-6, splitter:7-9</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>splitter:9-12</t>
+          <t>splitter:36-44</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>splitter:8, rast:1</t>
+          <t>splitter:10-12, rast:1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>splitter:15-19</t>
+          <t>splitter:55-65</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>splitter:24-30</t>
+          <t>splitter:85-100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>10</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>35</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung zum Lager bestimmt die Energie für den Weg: 20 Einheiten Entfernung = 1 Energie = 1 Minute.</t>
+          <t>Position auf der Karte in Prozent von Breite und Höhe (0 bis 100). Die Entfernung zum Lager bestimmt, wie lange der Weg dauert: 20 Einheiten Entfernung = 10 Sekunden. Wege kosten keine Energie.</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Energie für die Arbeit vor Ort bei Werten auf 1. Jeder Punkt Energie ist eine Minute: kosten 7 heißt 7 Minuten vor Ort. Hin- und Rückweg kommen nach Entfernung dazu. Der Wert Ausdauer bestimmt die Energieleiste: 10 Energie je Level.</t>
+          <t>Energie für die Arbeit vor Ort bei Werten auf 1. Jeder Punkt Energie dauert 10 Sekunden: kosten 6 heißt eine Minute vor Ort. Hin- und Rückweg dauern nach Entfernung, kosten aber keine Energie. Der Wert Ausdauer bestimmt die Energieleiste: 10 Energie je Level.</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Kosten: Material und Energie (zugleich Minuten), die der Bau braucht.</t>
+          <t>Kosten: Material und Energie (je Energie 10 Sekunden), die der Bau braucht.</t>
         </is>
       </c>
     </row>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2617,11 +2617,7 @@
           <t>nebelwaechter</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>kraft&gt;=3, ausdauer&gt;=3</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>splitter:3-4</t>
+          <t>splitter:6-8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>stein:4-6, splitter:7-9</t>
+          <t>stein:4-6, splitter:14-18</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>splitter:36-44</t>
+          <t>splitter:72-88</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>splitter:15, item:kopf_stirnband_1</t>
+          <t>splitter:30, item:kopf_stirnband_1</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>splitter:10-12, rast:1</t>
+          <t>splitter:20-24, rast:1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>splitter:20</t>
+          <t>splitter:40</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>splitter:30, item:handschuhe_griffhandschuhe_2</t>
+          <t>splitter:60, item:handschuhe_griffhandschuhe_2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>splitter:55-65</t>
+          <t>splitter:110-130</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>splitter:60, item:schuhe_leichtestiefel_3</t>
+          <t>splitter:120, item:schuhe_leichtestiefel_3</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>splitter:40</t>
+          <t>splitter:80</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>splitter:85-100</t>
+          <t>splitter:170-200</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -4364,7 +4364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4490,56 +4490,62 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>steinbank</t>
+          <t>lichterkette</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Steinbank</t>
+          <t>Lichterkette</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>haendler</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="H3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Eine Bank aus flachen Steinen, gerade breit genug für zwei.</t>
+          <t>Kleine bunte Lichter, quer übers Lager gespannt.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_steinbank.png</t>
+          <t>icon_einrichtung_lichterkette.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>wasserkrug</t>
+          <t>steinbank</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Wasserkrug</t>
+          <t>Steinbank</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -4550,55 +4556,51 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>stillesufer</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>selten</t>
-        </is>
-      </c>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Immer kühl, immer gefüllt.</t>
+          <t>Eine Bank aus flachen Steinen, gerade breit genug für zwei.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_wasserkrug.png</t>
+          <t>icon_einrichtung_steinbank.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>kraeuterbund</t>
+          <t>wasserkrug</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Kräuterbund</t>
+          <t>Wasserkrug</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>stillequelle</t>
+          <t>stillesufer</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4608,34 +4610,34 @@
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Riecht nach einem Sommer, den es hier nie gab.</t>
+          <t>Immer kühl, immer gefüllt.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_kraeuterbund.png</t>
+          <t>icon_einrichtung_wasserkrug.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>windspiel</t>
+          <t>kraeuterbund</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Windspiel</t>
+          <t>Kräuterbund</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -4646,12 +4648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>geister</t>
+          <t>stillequelle</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>sehr selten</t>
+          <t>selten</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -4659,173 +4661,173 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Klingt, bevor sich das Wetter ändert.</t>
+          <t>Riecht nach einem Sommer, den es hier nie gab.</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_windspiel.png</t>
+          <t>icon_einrichtung_kraeuterbund.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>teppich</t>
+          <t>windspiel</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Teppich</t>
+          <t>Windspiel</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>haendler</t>
+          <t>geister</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>selten</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>120</v>
-      </c>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Muster, in denen man sich verlieren kann.</t>
+          <t>Klingt, bevor sich das Wetter ändert.</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_teppich.png</t>
+          <t>icon_einrichtung_windspiel.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>kamin</t>
+          <t>teppich</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Kamin</t>
+          <t>Teppich</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>haendler</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="H8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Das Feuer zieht, der Rauch geht hinaus.</t>
+          <t>Muster, in denen man sich verlieren kann.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_kamin.png</t>
+          <t>icon_einrichtung_teppich.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>laterne</t>
+          <t>kamin</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Laterne</t>
+          <t>Kamin</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>langestrasse</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>sehr selten</t>
-        </is>
-      </c>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Wirft ein ruhiges Licht.</t>
+          <t>Das Feuer zieht, der Rauch geht hinaus.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_laterne.png</t>
+          <t>icon_einrichtung_kamin.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>leuchtmooskasten</t>
+          <t>laterne</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Leuchtmooskasten</t>
+          <t>Laterne</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -4836,7 +4838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>pilzhain</t>
+          <t>langestrasse</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4846,84 +4848,82 @@
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Ein Kasten voll Moos, das nachts leise leuchtet.</t>
+          <t>Wirft ein ruhiges Licht.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_leuchtmooskasten.png</t>
+          <t>icon_einrichtung_laterne.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>pilzholztisch</t>
+          <t>leuchtmooskasten</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Pilzholztisch</t>
+          <t>Leuchtmooskasten</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>haendler</t>
+          <t>pilzhain</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>selten</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>180</v>
-      </c>
+          <t>sehr selten</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Ein Tisch aus einem einzigen Pilzstiel.</t>
+          <t>Ein Kasten voll Moos, das nachts leise leuchtet.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_pilzholztisch.png</t>
+          <t>icon_einrichtung_leuchtmooskasten.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>regal</t>
+          <t>pilzholztisch</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Steinregal</t>
+          <t>Pilzholztisch</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -4934,44 +4934,46 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>steinbruch</t>
+          <t>haendler</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>sehr selten</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>selten</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>180</v>
+      </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Für alles, was man unterwegs findet.</t>
+          <t>Ein Tisch aus einem einzigen Pilzstiel.</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_regal.png</t>
+          <t>icon_einrichtung_pilzholztisch.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>wandbehang</t>
+          <t>regal</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Wandbehang</t>
+          <t>Steinregal</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -4982,7 +4984,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>q-furtwache</t>
+          <t>steinbruch</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -4995,47 +4997,47 @@
         <v>10</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Ein Tuch mit einem Muster aus Nebel und Wasser.</t>
+          <t>Für alles, was man unterwegs findet.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_wandbehang.png</t>
+          <t>icon_einrichtung_regal.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>nebelspiegel</t>
+          <t>wandbehang</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Nebelspiegel</t>
+          <t>Wandbehang</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>mondsee</t>
+          <t>q-furtwache</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>kostbar</t>
+          <t>sehr selten</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -5043,31 +5045,31 @@
         <v>10</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Ein Spiegel, in dem der Nebel stillsteht.</t>
+          <t>Ein Tuch mit einem Muster aus Nebel und Wasser.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_nebelspiegel.png</t>
+          <t>icon_einrichtung_wandbehang.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>sternkarte</t>
+          <t>nebelspiegel</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Sternkarte</t>
+          <t>Nebelspiegel</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -5078,92 +5080,92 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>q-mondnacht</t>
+          <t>mondsee</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>sehr selten</t>
+          <t>kostbar</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Die Sterne über dem Mondsee, Punkt für Punkt.</t>
+          <t>Ein Spiegel, in dem der Nebel stillsteht.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_sternkarte.png</t>
+          <t>icon_einrichtung_nebelspiegel.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>klangschale</t>
+          <t>sternkarte</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Klangschale</t>
+          <t>Sternkarte</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>echohoehle</t>
+          <t>q-mondnacht</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>selten</t>
+          <t>sehr selten</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>30</v>
-      </c>
       <c r="J16" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Ein Schlag, und der Ton bleibt lange im Raum.</t>
+          <t>Die Sterne über dem Mondsee, Punkt für Punkt.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>icon_einrichtung_klangschale.png</t>
+          <t>icon_einrichtung_sternkarte.png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>splitterschale</t>
+          <t>klangschale</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Splitterschale</t>
+          <t>Klangschale</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -5174,30 +5176,78 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>geister</t>
+          <t>echohoehle</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>kostbar</t>
+          <t>selten</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="J17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Ein Schlag, und der Ton bleibt lange im Raum.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>icon_einrichtung_klangschale.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>splitterschale</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Splitterschale</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>geister</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>kostbar</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>Eine Schale voller Bannsplitter, die nie ganz erlöschen.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>icon_einrichtung_splitterschale.png</t>
         </is>

--- a/data/welt.xlsx
+++ b/data/welt.xlsx
@@ -2006,16 +2006,16 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>kraft</t>
+          <t>beweglichkeit</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:7-9</t>
+          <t>pilzholz:6-8</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -2060,24 +2060,28 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>beweglichkeit&gt;=3</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>kraft, ausdauer</t>
+          <t>beweglichkeit, ausdauer</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>kraft</t>
+          <t>beweglichkeit</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:16-20</t>
+          <t>pilzholz:18-22</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2124,17 +2128,17 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>kraft&gt;=4</t>
+          <t>beweglichkeit&gt;=5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>kraft, ausdauer</t>
+          <t>beweglichkeit, ausdauer</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>kraft</t>
+          <t>beweglichkeit</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -2143,7 +2147,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>pilzholz:38-44</t>
+          <t>pilzholz:42-48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2197,11 +2201,11 @@
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>stein:7-9</t>
+          <t>stein:6-8</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2246,7 +2250,11 @@
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>kraft&gt;=3</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>kraft</t>
@@ -2259,11 +2267,11 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>stein:16-20</t>
+          <t>stein:18-22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2329,7 +2337,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>stein:38-44</t>
+          <t>stein:42-48</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
